--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121643203</v>
+        <v>121642666</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474542</v>
+        <v>475136</v>
       </c>
       <c r="R2" t="n">
-        <v>6784809</v>
+        <v>6784615</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642267</v>
+        <v>121642556</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475081</v>
+        <v>475112</v>
       </c>
       <c r="R3" t="n">
-        <v>6784478</v>
+        <v>6784581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642506</v>
+        <v>121642751</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,33 +907,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -942,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475110</v>
+        <v>475056</v>
       </c>
       <c r="R4" t="n">
-        <v>6784578</v>
+        <v>6784745</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642593</v>
+        <v>121641324</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,26 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1048,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475125</v>
+        <v>475075</v>
       </c>
       <c r="R5" t="n">
-        <v>6784604</v>
+        <v>6784468</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642942</v>
+        <v>121642955</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1154,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474753</v>
+        <v>474754</v>
       </c>
       <c r="R6" t="n">
-        <v>6784789</v>
+        <v>6784810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642928</v>
+        <v>121643189</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1260,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474760</v>
+        <v>474585</v>
       </c>
       <c r="R7" t="n">
-        <v>6784798</v>
+        <v>6784789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642587</v>
+        <v>121642761</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,26 +1335,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1366,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475118</v>
+        <v>475033</v>
       </c>
       <c r="R8" t="n">
-        <v>6784585</v>
+        <v>6784752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121643049</v>
+        <v>121642267</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,26 +1445,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474659</v>
+        <v>475081</v>
       </c>
       <c r="R9" t="n">
-        <v>6784800</v>
+        <v>6784478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1528,17 +1532,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642987</v>
+        <v>121642260</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,26 +1555,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474688</v>
+        <v>475080</v>
       </c>
       <c r="R10" t="n">
-        <v>6784772</v>
+        <v>6784480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1631,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,17 +1642,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642403</v>
+        <v>121642921</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,31 +1665,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1689,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475125</v>
+        <v>474804</v>
       </c>
       <c r="R11" t="n">
-        <v>6784471</v>
+        <v>6784818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,6 +1740,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642976</v>
+        <v>121642506</v>
       </c>
       <c r="B12" t="n">
-        <v>78650</v>
+        <v>90748</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,25 +1775,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1794,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474731</v>
+        <v>475110</v>
       </c>
       <c r="R12" t="n">
-        <v>6784765</v>
+        <v>6784578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121642791</v>
+        <v>121642493</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,26 +1889,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1900,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474995</v>
+        <v>475116</v>
       </c>
       <c r="R13" t="n">
-        <v>6784797</v>
+        <v>6784570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1965,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1963,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121643090</v>
+        <v>121642742</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,26 +1999,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2006,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474641</v>
+        <v>475084</v>
       </c>
       <c r="R14" t="n">
-        <v>6784795</v>
+        <v>6784706</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,7 +2075,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2069,10 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121643023</v>
+        <v>121641430</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,26 +2109,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474686</v>
+        <v>475085</v>
       </c>
       <c r="R15" t="n">
-        <v>6784780</v>
+        <v>6784456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2189,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2168,14 +2200,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642650</v>
+        <v>121642673</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2218,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475130</v>
+        <v>475137</v>
       </c>
       <c r="R16" t="n">
-        <v>6784606</v>
+        <v>6784616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2281,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642964</v>
+        <v>121642746</v>
       </c>
       <c r="B17" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,21 +2329,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2356,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474746</v>
+        <v>475079</v>
       </c>
       <c r="R17" t="n">
-        <v>6784772</v>
+        <v>6784712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2419,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642985</v>
+        <v>121642755</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2430,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474703</v>
+        <v>475045</v>
       </c>
       <c r="R18" t="n">
-        <v>6784764</v>
+        <v>6784754</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,14 +2518,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642847</v>
+        <v>121642869</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2536,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474825</v>
+        <v>474808</v>
       </c>
       <c r="R19" t="n">
-        <v>6784805</v>
+        <v>6784785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121642499</v>
+        <v>121642860</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2647,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2642,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475105</v>
+        <v>474820</v>
       </c>
       <c r="R20" t="n">
-        <v>6784582</v>
+        <v>6784784</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642673</v>
+        <v>121642976</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,21 +2757,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475137</v>
+        <v>474731</v>
       </c>
       <c r="R21" t="n">
-        <v>6784616</v>
+        <v>6784765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2847,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642308</v>
+        <v>121643037</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2859,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475127</v>
+        <v>474681</v>
       </c>
       <c r="R22" t="n">
-        <v>6784476</v>
+        <v>6784796</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121641430</v>
+        <v>121641316</v>
       </c>
       <c r="B23" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,33 +2973,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2973,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475085</v>
+        <v>475090</v>
       </c>
       <c r="R23" t="n">
-        <v>6784456</v>
+        <v>6784447</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642260</v>
+        <v>121642847</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,31 +3083,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3083,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475080</v>
+        <v>474825</v>
       </c>
       <c r="R24" t="n">
-        <v>6784480</v>
+        <v>6784805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,6 +3154,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3145,10 +3173,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642803</v>
+        <v>121642985</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3161,31 +3189,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3193,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474986</v>
+        <v>474703</v>
       </c>
       <c r="R25" t="n">
-        <v>6784798</v>
+        <v>6784764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,6 +3260,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3255,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121643182</v>
+        <v>121642403</v>
       </c>
       <c r="B26" t="n">
         <v>57357</v>
@@ -3303,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474609</v>
+        <v>475125</v>
       </c>
       <c r="R26" t="n">
-        <v>6784770</v>
+        <v>6784471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,10 +3389,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642718</v>
+        <v>121642881</v>
       </c>
       <c r="B27" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,33 +3405,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3417,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475154</v>
+        <v>474805</v>
       </c>
       <c r="R27" t="n">
-        <v>6784610</v>
+        <v>6784786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121641324</v>
+        <v>121642964</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,31 +3515,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3527,10 +3542,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475075</v>
+        <v>474746</v>
       </c>
       <c r="R28" t="n">
-        <v>6784468</v>
+        <v>6784772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,6 +3586,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3589,7 +3605,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642269</v>
+        <v>121642482</v>
       </c>
       <c r="B29" t="n">
         <v>57357</v>
@@ -3637,10 +3653,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475102</v>
+        <v>475111</v>
       </c>
       <c r="R29" t="n">
-        <v>6784483</v>
+        <v>6784565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,10 +3715,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642769</v>
+        <v>121642308</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,26 +3731,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3742,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475021</v>
+        <v>475127</v>
       </c>
       <c r="R30" t="n">
-        <v>6784769</v>
+        <v>6784476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3807,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3805,7 +3825,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642556</v>
+        <v>121642712</v>
       </c>
       <c r="B31" t="n">
         <v>57357</v>
@@ -3853,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475112</v>
+        <v>475147</v>
       </c>
       <c r="R31" t="n">
-        <v>6784581</v>
+        <v>6784617</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3915,7 +3935,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121643189</v>
+        <v>121642769</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3958,10 +3978,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474585</v>
+        <v>475021</v>
       </c>
       <c r="R32" t="n">
-        <v>6784789</v>
+        <v>6784769</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4021,7 +4041,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121642306</v>
+        <v>121643119</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4064,10 +4084,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475127</v>
+        <v>474609</v>
       </c>
       <c r="R33" t="n">
-        <v>6784476</v>
+        <v>6784770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,10 +4147,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642482</v>
+        <v>121642603</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,31 +4163,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4175,10 +4190,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475111</v>
+        <v>475130</v>
       </c>
       <c r="R34" t="n">
-        <v>6784565</v>
+        <v>6784603</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4219,6 +4234,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4237,7 +4253,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642735</v>
+        <v>121642928</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4280,10 +4296,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475086</v>
+        <v>474760</v>
       </c>
       <c r="R35" t="n">
-        <v>6784704</v>
+        <v>6784798</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,10 +4359,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642648</v>
+        <v>121642306</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4359,31 +4375,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4391,10 +4402,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475130</v>
+        <v>475127</v>
       </c>
       <c r="R36" t="n">
-        <v>6784606</v>
+        <v>6784476</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,6 +4446,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4453,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642712</v>
+        <v>121643093</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,31 +4481,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4501,10 +4508,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475147</v>
+        <v>474640</v>
       </c>
       <c r="R37" t="n">
-        <v>6784617</v>
+        <v>6784795</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4545,6 +4552,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4563,10 +4571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642869</v>
+        <v>121642648</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,26 +4587,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4606,10 +4619,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474808</v>
+        <v>475130</v>
       </c>
       <c r="R38" t="n">
-        <v>6784785</v>
+        <v>6784606</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4650,7 +4663,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4669,7 +4681,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642742</v>
+        <v>121642803</v>
       </c>
       <c r="B39" t="n">
         <v>57357</v>
@@ -4717,10 +4729,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475084</v>
+        <v>474986</v>
       </c>
       <c r="R39" t="n">
-        <v>6784706</v>
+        <v>6784798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4779,10 +4791,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642894</v>
+        <v>121642781</v>
       </c>
       <c r="B40" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4795,30 +4807,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4826,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474806</v>
+        <v>475004</v>
       </c>
       <c r="R40" t="n">
-        <v>6784787</v>
+        <v>6784792</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4870,7 +4883,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4889,10 +4901,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121643037</v>
+        <v>121642735</v>
       </c>
       <c r="B41" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4905,31 +4917,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4937,10 +4944,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474681</v>
+        <v>475086</v>
       </c>
       <c r="R41" t="n">
-        <v>6784796</v>
+        <v>6784704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4981,6 +4988,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4992,17 +5000,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121641316</v>
+        <v>121642718</v>
       </c>
       <c r="B42" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5015,29 +5023,33 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5047,10 +5059,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475090</v>
+        <v>475154</v>
       </c>
       <c r="R42" t="n">
-        <v>6784447</v>
+        <v>6784610</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5109,7 +5121,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121642603</v>
+        <v>121642601</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5152,7 +5164,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475130</v>
+        <v>475129</v>
       </c>
       <c r="R43" t="n">
         <v>6784603</v>
@@ -5215,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642493</v>
+        <v>121642499</v>
       </c>
       <c r="B44" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5231,31 +5243,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5263,10 +5270,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475116</v>
+        <v>475105</v>
       </c>
       <c r="R44" t="n">
-        <v>6784570</v>
+        <v>6784582</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5307,6 +5314,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5325,10 +5333,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121642781</v>
+        <v>121642894</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5341,31 +5349,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5373,10 +5380,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475004</v>
+        <v>474806</v>
       </c>
       <c r="R45" t="n">
-        <v>6784792</v>
+        <v>6784787</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5417,6 +5424,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5435,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642755</v>
+        <v>121643182</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,26 +5459,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5478,10 +5491,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475045</v>
+        <v>474609</v>
       </c>
       <c r="R46" t="n">
-        <v>6784754</v>
+        <v>6784770</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5522,7 +5535,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5541,10 +5553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642955</v>
+        <v>121642300</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5557,26 +5569,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5584,10 +5601,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474754</v>
+        <v>475106</v>
       </c>
       <c r="R47" t="n">
-        <v>6784810</v>
+        <v>6784487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,7 +5645,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5647,10 +5663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121642881</v>
+        <v>121642650</v>
       </c>
       <c r="B48" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,31 +5679,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5695,10 +5706,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474805</v>
+        <v>475130</v>
       </c>
       <c r="R48" t="n">
-        <v>6784786</v>
+        <v>6784606</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,6 +5750,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5757,10 +5769,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642761</v>
+        <v>121643203</v>
       </c>
       <c r="B49" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5773,31 +5785,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5805,10 +5812,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475033</v>
+        <v>474542</v>
       </c>
       <c r="R49" t="n">
-        <v>6784752</v>
+        <v>6784809</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5849,6 +5856,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5867,10 +5875,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642666</v>
+        <v>121643049</v>
       </c>
       <c r="B50" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5879,25 +5887,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5910,10 +5918,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475136</v>
+        <v>474659</v>
       </c>
       <c r="R50" t="n">
-        <v>6784615</v>
+        <v>6784800</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5973,10 +5981,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642860</v>
+        <v>121642942</v>
       </c>
       <c r="B51" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5989,29 +5997,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -6020,10 +6024,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474820</v>
+        <v>474753</v>
       </c>
       <c r="R51" t="n">
-        <v>6784784</v>
+        <v>6784789</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6083,7 +6087,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121643103</v>
+        <v>121643090</v>
       </c>
       <c r="B52" t="n">
         <v>78616</v>
@@ -6126,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474609</v>
+        <v>474641</v>
       </c>
       <c r="R52" t="n">
-        <v>6784770</v>
+        <v>6784795</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6189,7 +6193,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642490</v>
+        <v>121642729</v>
       </c>
       <c r="B53" t="n">
         <v>78616</v>
@@ -6232,10 +6236,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475112</v>
+        <v>475088</v>
       </c>
       <c r="R53" t="n">
-        <v>6784571</v>
+        <v>6784704</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6295,7 +6299,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642601</v>
+        <v>121643023</v>
       </c>
       <c r="B54" t="n">
         <v>78616</v>
@@ -6338,10 +6342,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475129</v>
+        <v>474686</v>
       </c>
       <c r="R54" t="n">
-        <v>6784603</v>
+        <v>6784780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6401,7 +6405,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642746</v>
+        <v>121642791</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6444,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475079</v>
+        <v>474995</v>
       </c>
       <c r="R55" t="n">
-        <v>6784712</v>
+        <v>6784797</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6507,10 +6511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642300</v>
+        <v>121642660</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6523,31 +6527,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6555,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475106</v>
+        <v>475110</v>
       </c>
       <c r="R56" t="n">
-        <v>6784487</v>
+        <v>6784606</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6599,6 +6598,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642921</v>
+        <v>121642987</v>
       </c>
       <c r="B57" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6633,29 +6633,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6664,10 +6660,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474804</v>
+        <v>474688</v>
       </c>
       <c r="R57" t="n">
-        <v>6784818</v>
+        <v>6784772</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6727,7 +6723,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642729</v>
+        <v>121642593</v>
       </c>
       <c r="B58" t="n">
         <v>78616</v>
@@ -6770,10 +6766,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475088</v>
+        <v>475125</v>
       </c>
       <c r="R58" t="n">
-        <v>6784704</v>
+        <v>6784604</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6833,10 +6829,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642751</v>
+        <v>121642269</v>
       </c>
       <c r="B59" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6849,26 +6845,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6876,10 +6877,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475056</v>
+        <v>475102</v>
       </c>
       <c r="R59" t="n">
-        <v>6784745</v>
+        <v>6784483</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6920,7 +6921,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6939,7 +6939,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121642660</v>
+        <v>121642490</v>
       </c>
       <c r="B60" t="n">
         <v>78616</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475110</v>
+        <v>475112</v>
       </c>
       <c r="R60" t="n">
-        <v>6784606</v>
+        <v>6784571</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7045,7 +7045,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121643093</v>
+        <v>121642587</v>
       </c>
       <c r="B61" t="n">
         <v>78616</v>
@@ -7088,10 +7088,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474640</v>
+        <v>475118</v>
       </c>
       <c r="R61" t="n">
-        <v>6784795</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7261,6 +7261,324 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121807149</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>475105</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6784482</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121807181</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>475055</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6784636</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121807130</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>475111</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6784416</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642482</v>
+        <v>121642769</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,31 +3621,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3653,10 +3648,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475111</v>
+        <v>475021</v>
       </c>
       <c r="R29" t="n">
-        <v>6784565</v>
+        <v>6784769</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3697,6 +3692,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3715,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642308</v>
+        <v>121643119</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,31 +3727,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3763,10 +3754,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475127</v>
+        <v>474609</v>
       </c>
       <c r="R30" t="n">
-        <v>6784476</v>
+        <v>6784770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3807,6 +3798,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3825,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642712</v>
+        <v>121642603</v>
       </c>
       <c r="B31" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,31 +3833,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3873,10 +3860,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475147</v>
+        <v>475130</v>
       </c>
       <c r="R31" t="n">
-        <v>6784617</v>
+        <v>6784603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,6 +3904,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3935,7 +3923,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121642769</v>
+        <v>121642928</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3978,10 +3966,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475021</v>
+        <v>474760</v>
       </c>
       <c r="R32" t="n">
-        <v>6784769</v>
+        <v>6784798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4029,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121643119</v>
+        <v>121642306</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4084,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474609</v>
+        <v>475127</v>
       </c>
       <c r="R33" t="n">
-        <v>6784770</v>
+        <v>6784476</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4147,7 +4135,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642603</v>
+        <v>121643093</v>
       </c>
       <c r="B34" t="n">
         <v>78616</v>
@@ -4190,10 +4178,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475130</v>
+        <v>474640</v>
       </c>
       <c r="R34" t="n">
-        <v>6784603</v>
+        <v>6784795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4253,10 +4241,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642928</v>
+        <v>121642482</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,26 +4257,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4296,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474760</v>
+        <v>475111</v>
       </c>
       <c r="R35" t="n">
-        <v>6784798</v>
+        <v>6784565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4340,7 +4333,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4359,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642306</v>
+        <v>121642308</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4375,26 +4367,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4446,7 +4443,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4465,10 +4461,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121643093</v>
+        <v>121642712</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4481,26 +4477,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4508,10 +4509,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474640</v>
+        <v>475147</v>
       </c>
       <c r="R37" t="n">
-        <v>6784795</v>
+        <v>6784617</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4552,7 +4553,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642648</v>
+        <v>121642735</v>
       </c>
       <c r="B38" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4587,31 +4587,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475130</v>
+        <v>475086</v>
       </c>
       <c r="R38" t="n">
-        <v>6784606</v>
+        <v>6784704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4663,6 +4658,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4681,7 +4677,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642803</v>
+        <v>121642648</v>
       </c>
       <c r="B39" t="n">
         <v>57357</v>
@@ -4729,10 +4725,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474986</v>
+        <v>475130</v>
       </c>
       <c r="R39" t="n">
-        <v>6784798</v>
+        <v>6784606</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4791,7 +4787,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642781</v>
+        <v>121642803</v>
       </c>
       <c r="B40" t="n">
         <v>57357</v>
@@ -4839,10 +4835,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475004</v>
+        <v>474986</v>
       </c>
       <c r="R40" t="n">
-        <v>6784792</v>
+        <v>6784798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,10 +4897,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642735</v>
+        <v>121642781</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,26 +4913,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4944,10 +4945,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475086</v>
+        <v>475004</v>
       </c>
       <c r="R41" t="n">
-        <v>6784704</v>
+        <v>6784792</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4988,7 +4989,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807149</v>
+        <v>121807181</v>
       </c>
       <c r="B63" t="n">
         <v>78616</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475105</v>
+        <v>475055</v>
       </c>
       <c r="R63" t="n">
-        <v>6784482</v>
+        <v>6784636</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807181</v>
+        <v>121807130</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475055</v>
+        <v>475111</v>
       </c>
       <c r="R64" t="n">
-        <v>6784636</v>
+        <v>6784416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807130</v>
+        <v>121807149</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475111</v>
+        <v>475105</v>
       </c>
       <c r="R65" t="n">
-        <v>6784416</v>
+        <v>6784482</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121642666</v>
+        <v>121642942</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475136</v>
+        <v>474753</v>
       </c>
       <c r="R2" t="n">
-        <v>6784615</v>
+        <v>6784789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642556</v>
+        <v>121642735</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475112</v>
+        <v>475086</v>
       </c>
       <c r="R3" t="n">
-        <v>6784581</v>
+        <v>6784704</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642751</v>
+        <v>121642987</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475056</v>
+        <v>474688</v>
       </c>
       <c r="R4" t="n">
-        <v>6784745</v>
+        <v>6784772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641324</v>
+        <v>121642260</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1045,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475075</v>
+        <v>475080</v>
       </c>
       <c r="R5" t="n">
-        <v>6784468</v>
+        <v>6784480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642955</v>
+        <v>121642712</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,26 +1119,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474754</v>
+        <v>475147</v>
       </c>
       <c r="R6" t="n">
-        <v>6784810</v>
+        <v>6784617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121643189</v>
+        <v>121642976</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474585</v>
+        <v>474731</v>
       </c>
       <c r="R7" t="n">
-        <v>6784789</v>
+        <v>6784765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642761</v>
+        <v>121642881</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475033</v>
+        <v>474805</v>
       </c>
       <c r="R8" t="n">
-        <v>6784752</v>
+        <v>6784786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642267</v>
+        <v>121642660</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,31 +1445,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475081</v>
+        <v>475110</v>
       </c>
       <c r="R9" t="n">
-        <v>6784478</v>
+        <v>6784606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,6 +1516,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642260</v>
+        <v>121642593</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,31 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475080</v>
+        <v>475125</v>
       </c>
       <c r="R10" t="n">
-        <v>6784480</v>
+        <v>6784604</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1649,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642921</v>
+        <v>121643049</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,29 +1657,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1696,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474804</v>
+        <v>474659</v>
       </c>
       <c r="R11" t="n">
-        <v>6784818</v>
+        <v>6784800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642506</v>
+        <v>121642964</v>
       </c>
       <c r="B12" t="n">
-        <v>90748</v>
+        <v>78650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,33 +1763,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1810,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475110</v>
+        <v>474746</v>
       </c>
       <c r="R12" t="n">
-        <v>6784578</v>
+        <v>6784772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121642493</v>
+        <v>121642506</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>90748</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,31 +1869,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1921,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475116</v>
+        <v>475110</v>
       </c>
       <c r="R13" t="n">
-        <v>6784570</v>
+        <v>6784578</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,6 +1948,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121642742</v>
+        <v>121642769</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,31 +1983,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2031,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475084</v>
+        <v>475021</v>
       </c>
       <c r="R14" t="n">
-        <v>6784706</v>
+        <v>6784769</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,6 +2054,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2093,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121641430</v>
+        <v>121642847</v>
       </c>
       <c r="B15" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,35 +2089,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2145,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475085</v>
+        <v>474825</v>
       </c>
       <c r="R15" t="n">
-        <v>6784456</v>
+        <v>6784805</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,6 +2160,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2207,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642673</v>
+        <v>121642403</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,26 +2195,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2250,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475137</v>
+        <v>475125</v>
       </c>
       <c r="R16" t="n">
-        <v>6784616</v>
+        <v>6784471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,7 +2271,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,7 +2289,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642746</v>
+        <v>121642928</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2356,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475079</v>
+        <v>474760</v>
       </c>
       <c r="R17" t="n">
-        <v>6784712</v>
+        <v>6784798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642755</v>
+        <v>121642650</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2462,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475045</v>
+        <v>475130</v>
       </c>
       <c r="R18" t="n">
-        <v>6784754</v>
+        <v>6784606</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,7 +2501,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642869</v>
+        <v>121642306</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2568,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474808</v>
+        <v>475127</v>
       </c>
       <c r="R19" t="n">
-        <v>6784785</v>
+        <v>6784476</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121642860</v>
+        <v>121642781</v>
       </c>
       <c r="B20" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,30 +2623,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2678,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474820</v>
+        <v>475004</v>
       </c>
       <c r="R20" t="n">
-        <v>6784784</v>
+        <v>6784792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,7 +2699,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2741,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642976</v>
+        <v>121642300</v>
       </c>
       <c r="B21" t="n">
-        <v>78650</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,26 +2733,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2784,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474731</v>
+        <v>475106</v>
       </c>
       <c r="R21" t="n">
-        <v>6784765</v>
+        <v>6784487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2809,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121643037</v>
+        <v>121641430</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2863,29 +2843,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2895,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474681</v>
+        <v>475085</v>
       </c>
       <c r="R22" t="n">
-        <v>6784796</v>
+        <v>6784456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2957,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121641316</v>
+        <v>121642499</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2973,31 +2957,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3005,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475090</v>
+        <v>475105</v>
       </c>
       <c r="R23" t="n">
-        <v>6784447</v>
+        <v>6784582</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3049,6 +3028,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3067,7 +3047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642847</v>
+        <v>121643119</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3110,10 +3090,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474825</v>
+        <v>474609</v>
       </c>
       <c r="R24" t="n">
-        <v>6784805</v>
+        <v>6784770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,7 +3153,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642985</v>
+        <v>121642603</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3216,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474703</v>
+        <v>475130</v>
       </c>
       <c r="R25" t="n">
-        <v>6784764</v>
+        <v>6784603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3259,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642403</v>
+        <v>121642746</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,31 +3275,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3327,10 +3302,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475125</v>
+        <v>475079</v>
       </c>
       <c r="R26" t="n">
-        <v>6784471</v>
+        <v>6784712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3371,6 +3346,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3389,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642881</v>
+        <v>121643093</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,31 +3381,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3437,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474805</v>
+        <v>474640</v>
       </c>
       <c r="R27" t="n">
-        <v>6784786</v>
+        <v>6784795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,6 +3452,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3499,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642964</v>
+        <v>121642556</v>
       </c>
       <c r="B28" t="n">
-        <v>78650</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,26 +3487,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3542,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474746</v>
+        <v>475112</v>
       </c>
       <c r="R28" t="n">
-        <v>6784772</v>
+        <v>6784581</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3586,7 +3563,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3605,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642769</v>
+        <v>121642803</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,26 +3597,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3648,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475021</v>
+        <v>474986</v>
       </c>
       <c r="R29" t="n">
-        <v>6784769</v>
+        <v>6784798</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3692,7 +3673,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3711,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121643119</v>
+        <v>121642269</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,26 +3707,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3754,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474609</v>
+        <v>475102</v>
       </c>
       <c r="R30" t="n">
-        <v>6784770</v>
+        <v>6784483</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3783,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3817,7 +3801,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642603</v>
+        <v>121642791</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -3860,10 +3844,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475130</v>
+        <v>474995</v>
       </c>
       <c r="R31" t="n">
-        <v>6784603</v>
+        <v>6784797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3923,7 +3907,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121642928</v>
+        <v>121642673</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3966,10 +3950,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474760</v>
+        <v>475137</v>
       </c>
       <c r="R32" t="n">
-        <v>6784798</v>
+        <v>6784616</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,7 +4013,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121642306</v>
+        <v>121643023</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4072,10 +4056,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475127</v>
+        <v>474686</v>
       </c>
       <c r="R33" t="n">
-        <v>6784476</v>
+        <v>6784780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,7 +4119,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121643093</v>
+        <v>121642985</v>
       </c>
       <c r="B34" t="n">
         <v>78616</v>
@@ -4178,10 +4162,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474640</v>
+        <v>474703</v>
       </c>
       <c r="R34" t="n">
-        <v>6784795</v>
+        <v>6784764</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642482</v>
+        <v>121642869</v>
       </c>
       <c r="B35" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,31 +4241,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4289,10 +4268,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475111</v>
+        <v>474808</v>
       </c>
       <c r="R35" t="n">
-        <v>6784565</v>
+        <v>6784785</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4333,6 +4312,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4351,10 +4331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642308</v>
+        <v>121642921</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4367,31 +4347,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4399,10 +4378,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475127</v>
+        <v>474804</v>
       </c>
       <c r="R36" t="n">
-        <v>6784476</v>
+        <v>6784818</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,6 +4422,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4461,10 +4441,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642712</v>
+        <v>121642666</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,35 +4453,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4509,10 +4484,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475147</v>
+        <v>475136</v>
       </c>
       <c r="R37" t="n">
-        <v>6784617</v>
+        <v>6784615</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4553,6 +4528,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4571,7 +4547,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642735</v>
+        <v>121642601</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -4614,10 +4590,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475086</v>
+        <v>475129</v>
       </c>
       <c r="R38" t="n">
-        <v>6784704</v>
+        <v>6784603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642648</v>
+        <v>121642751</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4693,31 +4669,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4725,10 +4696,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475130</v>
+        <v>475056</v>
       </c>
       <c r="R39" t="n">
-        <v>6784606</v>
+        <v>6784745</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,6 +4740,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4787,7 +4759,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642803</v>
+        <v>121642482</v>
       </c>
       <c r="B40" t="n">
         <v>57357</v>
@@ -4835,10 +4807,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474986</v>
+        <v>475111</v>
       </c>
       <c r="R40" t="n">
-        <v>6784798</v>
+        <v>6784565</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4897,7 +4869,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642781</v>
+        <v>121641324</v>
       </c>
       <c r="B41" t="n">
         <v>57357</v>
@@ -4945,10 +4917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475004</v>
+        <v>475075</v>
       </c>
       <c r="R41" t="n">
-        <v>6784792</v>
+        <v>6784468</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5007,10 +4979,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121642718</v>
+        <v>121642742</v>
       </c>
       <c r="B42" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5023,33 +4995,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5059,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475154</v>
+        <v>475084</v>
       </c>
       <c r="R42" t="n">
-        <v>6784610</v>
+        <v>6784706</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5121,7 +5089,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121642601</v>
+        <v>121643203</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5164,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475129</v>
+        <v>474542</v>
       </c>
       <c r="R43" t="n">
-        <v>6784603</v>
+        <v>6784809</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642499</v>
+        <v>121642761</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5243,26 +5211,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5270,10 +5243,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475105</v>
+        <v>475033</v>
       </c>
       <c r="R44" t="n">
-        <v>6784582</v>
+        <v>6784752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,7 +5287,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5333,10 +5305,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121642894</v>
+        <v>121643182</v>
       </c>
       <c r="B45" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5349,30 +5321,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5380,10 +5353,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474806</v>
+        <v>474609</v>
       </c>
       <c r="R45" t="n">
-        <v>6784787</v>
+        <v>6784770</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5424,7 +5397,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5443,10 +5415,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121643182</v>
+        <v>121642718</v>
       </c>
       <c r="B46" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5459,29 +5431,33 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5491,10 +5467,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474609</v>
+        <v>475154</v>
       </c>
       <c r="R46" t="n">
-        <v>6784770</v>
+        <v>6784610</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5553,10 +5529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642300</v>
+        <v>121642955</v>
       </c>
       <c r="B47" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5569,31 +5545,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5601,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475106</v>
+        <v>474754</v>
       </c>
       <c r="R47" t="n">
-        <v>6784487</v>
+        <v>6784810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5645,6 +5616,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5663,7 +5635,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121642650</v>
+        <v>121643090</v>
       </c>
       <c r="B48" t="n">
         <v>78616</v>
@@ -5706,10 +5678,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475130</v>
+        <v>474641</v>
       </c>
       <c r="R48" t="n">
-        <v>6784606</v>
+        <v>6784795</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5769,10 +5741,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121643203</v>
+        <v>121642894</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5785,25 +5757,29 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5812,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474542</v>
+        <v>474806</v>
       </c>
       <c r="R49" t="n">
-        <v>6784809</v>
+        <v>6784787</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5875,7 +5851,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121643049</v>
+        <v>121642490</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5918,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474659</v>
+        <v>475112</v>
       </c>
       <c r="R50" t="n">
-        <v>6784800</v>
+        <v>6784571</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5981,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642942</v>
+        <v>121642493</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5997,26 +5973,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6024,10 +6005,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474753</v>
+        <v>475116</v>
       </c>
       <c r="R51" t="n">
-        <v>6784789</v>
+        <v>6784570</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,7 +6049,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6087,7 +6067,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121643090</v>
+        <v>121642729</v>
       </c>
       <c r="B52" t="n">
         <v>78616</v>
@@ -6130,10 +6110,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474641</v>
+        <v>475088</v>
       </c>
       <c r="R52" t="n">
-        <v>6784795</v>
+        <v>6784704</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6173,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642729</v>
+        <v>121643189</v>
       </c>
       <c r="B53" t="n">
         <v>78616</v>
@@ -6236,10 +6216,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475088</v>
+        <v>474585</v>
       </c>
       <c r="R53" t="n">
-        <v>6784704</v>
+        <v>6784789</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,10 +6279,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121643023</v>
+        <v>121642267</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6315,26 +6295,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6342,10 +6327,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474686</v>
+        <v>475081</v>
       </c>
       <c r="R54" t="n">
-        <v>6784780</v>
+        <v>6784478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6386,7 +6371,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6405,10 +6389,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642791</v>
+        <v>121642308</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6421,26 +6405,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6448,10 +6437,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474995</v>
+        <v>475127</v>
       </c>
       <c r="R55" t="n">
-        <v>6784797</v>
+        <v>6784476</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6492,7 +6481,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6511,10 +6499,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642660</v>
+        <v>121641316</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6527,26 +6515,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6554,10 +6547,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475110</v>
+        <v>475090</v>
       </c>
       <c r="R56" t="n">
-        <v>6784606</v>
+        <v>6784447</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6598,7 +6591,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6617,7 +6609,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642987</v>
+        <v>121642755</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6660,10 +6652,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474688</v>
+        <v>475045</v>
       </c>
       <c r="R57" t="n">
-        <v>6784772</v>
+        <v>6784754</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6723,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642593</v>
+        <v>121642648</v>
       </c>
       <c r="B58" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6739,26 +6731,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6766,10 +6763,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475125</v>
+        <v>475130</v>
       </c>
       <c r="R58" t="n">
-        <v>6784604</v>
+        <v>6784606</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6810,7 +6807,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6829,10 +6825,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642269</v>
+        <v>121642860</v>
       </c>
       <c r="B59" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6845,31 +6841,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6877,10 +6872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475102</v>
+        <v>474820</v>
       </c>
       <c r="R59" t="n">
-        <v>6784483</v>
+        <v>6784784</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6921,6 +6916,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6939,7 +6935,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121642490</v>
+        <v>121642587</v>
       </c>
       <c r="B60" t="n">
         <v>78616</v>
@@ -6982,10 +6978,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475112</v>
+        <v>475118</v>
       </c>
       <c r="R60" t="n">
-        <v>6784571</v>
+        <v>6784585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7045,10 +7041,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121642587</v>
+        <v>121643037</v>
       </c>
       <c r="B61" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,26 +7057,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7088,10 +7089,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475118</v>
+        <v>474681</v>
       </c>
       <c r="R61" t="n">
-        <v>6784585</v>
+        <v>6784796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7132,7 +7133,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807130</v>
+        <v>121807149</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475111</v>
+        <v>475105</v>
       </c>
       <c r="R64" t="n">
-        <v>6784416</v>
+        <v>6784482</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807149</v>
+        <v>121807130</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475105</v>
+        <v>475111</v>
       </c>
       <c r="R65" t="n">
-        <v>6784482</v>
+        <v>6784416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642712</v>
+        <v>121642976</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,31 +1119,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475147</v>
+        <v>474731</v>
       </c>
       <c r="R6" t="n">
-        <v>6784617</v>
+        <v>6784765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1190,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642976</v>
+        <v>121642712</v>
       </c>
       <c r="B7" t="n">
-        <v>78650</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,26 +1225,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474731</v>
+        <v>475147</v>
       </c>
       <c r="R7" t="n">
-        <v>6784765</v>
+        <v>6784617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642881</v>
+        <v>121643049</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,31 +1335,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474805</v>
+        <v>474659</v>
       </c>
       <c r="R8" t="n">
-        <v>6784786</v>
+        <v>6784800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1406,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642660</v>
+        <v>121642964</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475110</v>
+        <v>474746</v>
       </c>
       <c r="R9" t="n">
-        <v>6784606</v>
+        <v>6784772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1535,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642593</v>
+        <v>121642660</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1578,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475125</v>
+        <v>475110</v>
       </c>
       <c r="R10" t="n">
-        <v>6784604</v>
+        <v>6784606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121643049</v>
+        <v>121642593</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474659</v>
+        <v>475125</v>
       </c>
       <c r="R11" t="n">
-        <v>6784800</v>
+        <v>6784604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642964</v>
+        <v>121642881</v>
       </c>
       <c r="B12" t="n">
-        <v>78650</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,26 +1759,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1790,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474746</v>
+        <v>474805</v>
       </c>
       <c r="R12" t="n">
-        <v>6784772</v>
+        <v>6784786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1835,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642921</v>
+        <v>121642666</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4343,33 +4343,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4378,10 +4374,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>474804</v>
+        <v>475136</v>
       </c>
       <c r="R36" t="n">
-        <v>6784818</v>
+        <v>6784615</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,10 +4437,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642666</v>
+        <v>121642601</v>
       </c>
       <c r="B37" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4453,25 +4449,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4484,10 +4480,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475136</v>
+        <v>475129</v>
       </c>
       <c r="R37" t="n">
-        <v>6784615</v>
+        <v>6784603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4547,7 +4543,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642601</v>
+        <v>121642751</v>
       </c>
       <c r="B38" t="n">
         <v>78616</v>
@@ -4590,10 +4586,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475129</v>
+        <v>475056</v>
       </c>
       <c r="R38" t="n">
-        <v>6784603</v>
+        <v>6784745</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,10 +4649,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642751</v>
+        <v>121642482</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4669,26 +4665,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4696,10 +4697,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475056</v>
+        <v>475111</v>
       </c>
       <c r="R39" t="n">
-        <v>6784745</v>
+        <v>6784565</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4740,7 +4741,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642482</v>
+        <v>121641324</v>
       </c>
       <c r="B40" t="n">
         <v>57357</v>
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475111</v>
+        <v>475075</v>
       </c>
       <c r="R40" t="n">
-        <v>6784565</v>
+        <v>6784468</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121641324</v>
+        <v>121642921</v>
       </c>
       <c r="B41" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4885,31 +4885,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4917,10 +4916,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475075</v>
+        <v>474804</v>
       </c>
       <c r="R41" t="n">
-        <v>6784468</v>
+        <v>6784818</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4961,6 +4960,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -6935,10 +6935,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121642587</v>
+        <v>121643037</v>
       </c>
       <c r="B60" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6951,26 +6951,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475118</v>
+        <v>474681</v>
       </c>
       <c r="R60" t="n">
-        <v>6784585</v>
+        <v>6784796</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7022,7 +7027,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7041,10 +7045,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121643037</v>
+        <v>121642587</v>
       </c>
       <c r="B61" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7057,31 +7061,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7089,10 +7088,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474681</v>
+        <v>475118</v>
       </c>
       <c r="R61" t="n">
-        <v>6784796</v>
+        <v>6784585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7133,6 +7132,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121642942</v>
+        <v>121642976</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474753</v>
+        <v>474731</v>
       </c>
       <c r="R2" t="n">
-        <v>6784789</v>
+        <v>6784765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642735</v>
+        <v>121642881</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475086</v>
+        <v>474805</v>
       </c>
       <c r="R3" t="n">
-        <v>6784704</v>
+        <v>6784786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642987</v>
+        <v>121642761</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +907,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474688</v>
+        <v>475033</v>
       </c>
       <c r="R4" t="n">
-        <v>6784772</v>
+        <v>6784752</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642260</v>
+        <v>121642928</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,31 +1017,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475080</v>
+        <v>474760</v>
       </c>
       <c r="R5" t="n">
-        <v>6784480</v>
+        <v>6784798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1088,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642976</v>
+        <v>121642593</v>
       </c>
       <c r="B6" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474731</v>
+        <v>475125</v>
       </c>
       <c r="R6" t="n">
-        <v>6784765</v>
+        <v>6784604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642712</v>
+        <v>121642964</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,31 +1229,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475147</v>
+        <v>474746</v>
       </c>
       <c r="R7" t="n">
-        <v>6784617</v>
+        <v>6784772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121643049</v>
+        <v>121642781</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,26 +1335,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474659</v>
+        <v>475004</v>
       </c>
       <c r="R8" t="n">
-        <v>6784800</v>
+        <v>6784792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1411,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1425,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642964</v>
+        <v>121642860</v>
       </c>
       <c r="B9" t="n">
-        <v>78650</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,25 +1445,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1468,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474746</v>
+        <v>474820</v>
       </c>
       <c r="R9" t="n">
-        <v>6784772</v>
+        <v>6784784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642660</v>
+        <v>121641430</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,26 +1555,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475110</v>
+        <v>475085</v>
       </c>
       <c r="R10" t="n">
-        <v>6784606</v>
+        <v>6784456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1635,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1637,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642593</v>
+        <v>121642300</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,26 +1669,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475125</v>
+        <v>475106</v>
       </c>
       <c r="R11" t="n">
-        <v>6784604</v>
+        <v>6784487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1745,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1743,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642881</v>
+        <v>121643093</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,31 +1779,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474805</v>
+        <v>474640</v>
       </c>
       <c r="R12" t="n">
-        <v>6784786</v>
+        <v>6784795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,6 +1850,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1853,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121642506</v>
+        <v>121642660</v>
       </c>
       <c r="B13" t="n">
-        <v>90748</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,33 +1885,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1907,7 +1915,7 @@
         <v>475110</v>
       </c>
       <c r="R13" t="n">
-        <v>6784578</v>
+        <v>6784606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121642769</v>
+        <v>121643049</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2010,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475021</v>
+        <v>474659</v>
       </c>
       <c r="R14" t="n">
-        <v>6784769</v>
+        <v>6784800</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121642847</v>
+        <v>121642269</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,26 +2097,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2116,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474825</v>
+        <v>475102</v>
       </c>
       <c r="R15" t="n">
-        <v>6784805</v>
+        <v>6784483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2289,7 +2301,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642928</v>
+        <v>121642499</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2332,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474760</v>
+        <v>475105</v>
       </c>
       <c r="R17" t="n">
-        <v>6784798</v>
+        <v>6784582</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642650</v>
+        <v>121641316</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,26 +2423,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2438,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475130</v>
+        <v>475090</v>
       </c>
       <c r="R18" t="n">
-        <v>6784606</v>
+        <v>6784447</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2499,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2501,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642306</v>
+        <v>121643037</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,26 +2533,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2544,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475127</v>
+        <v>474681</v>
       </c>
       <c r="R19" t="n">
-        <v>6784476</v>
+        <v>6784796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2609,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2607,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121642781</v>
+        <v>121643119</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,31 +2643,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2655,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475004</v>
+        <v>474609</v>
       </c>
       <c r="R20" t="n">
-        <v>6784792</v>
+        <v>6784770</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2714,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2717,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642300</v>
+        <v>121642647</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,31 +2749,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2765,10 +2776,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475106</v>
+        <v>475130</v>
       </c>
       <c r="R21" t="n">
-        <v>6784487</v>
+        <v>6784606</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,6 +2820,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2827,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121641430</v>
+        <v>121642648</v>
       </c>
       <c r="B22" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,33 +2855,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2879,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475085</v>
+        <v>475130</v>
       </c>
       <c r="R22" t="n">
-        <v>6784456</v>
+        <v>6784606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642499</v>
+        <v>121642718</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,26 +2965,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2984,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475105</v>
+        <v>475154</v>
       </c>
       <c r="R23" t="n">
-        <v>6784582</v>
+        <v>6784610</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,7 +3045,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3047,7 +3063,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121643119</v>
+        <v>121642306</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3090,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474609</v>
+        <v>475127</v>
       </c>
       <c r="R24" t="n">
-        <v>6784770</v>
+        <v>6784476</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3153,7 +3169,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642603</v>
+        <v>121642735</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3196,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475130</v>
+        <v>475086</v>
       </c>
       <c r="R25" t="n">
-        <v>6784603</v>
+        <v>6784704</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3275,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642746</v>
+        <v>121642673</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3302,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475079</v>
+        <v>475137</v>
       </c>
       <c r="R26" t="n">
-        <v>6784712</v>
+        <v>6784616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121643093</v>
+        <v>121642921</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,25 +3397,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3408,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474640</v>
+        <v>474804</v>
       </c>
       <c r="R27" t="n">
-        <v>6784795</v>
+        <v>6784818</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642556</v>
+        <v>121642493</v>
       </c>
       <c r="B28" t="n">
         <v>57357</v>
@@ -3519,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475112</v>
+        <v>475116</v>
       </c>
       <c r="R28" t="n">
-        <v>6784581</v>
+        <v>6784570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,10 +3601,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642803</v>
+        <v>121642601</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3597,31 +3617,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3629,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474986</v>
+        <v>475129</v>
       </c>
       <c r="R29" t="n">
-        <v>6784798</v>
+        <v>6784603</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3673,6 +3688,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3691,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642269</v>
+        <v>121642985</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,31 +3723,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3739,10 +3750,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475102</v>
+        <v>474703</v>
       </c>
       <c r="R30" t="n">
-        <v>6784483</v>
+        <v>6784764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,6 +3794,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3801,7 +3813,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642791</v>
+        <v>121642955</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -3844,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474995</v>
+        <v>474754</v>
       </c>
       <c r="R31" t="n">
-        <v>6784797</v>
+        <v>6784810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3907,7 +3919,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121642673</v>
+        <v>121643090</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3950,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475137</v>
+        <v>474641</v>
       </c>
       <c r="R32" t="n">
-        <v>6784616</v>
+        <v>6784795</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4013,7 +4025,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121643023</v>
+        <v>121642490</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4056,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474686</v>
+        <v>475112</v>
       </c>
       <c r="R33" t="n">
-        <v>6784780</v>
+        <v>6784571</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4119,10 +4131,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642985</v>
+        <v>121642482</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4135,26 +4147,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4162,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474703</v>
+        <v>475111</v>
       </c>
       <c r="R34" t="n">
-        <v>6784764</v>
+        <v>6784565</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,7 +4223,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4225,7 +4241,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642869</v>
+        <v>121642603</v>
       </c>
       <c r="B35" t="n">
         <v>78616</v>
@@ -4268,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474808</v>
+        <v>475130</v>
       </c>
       <c r="R35" t="n">
-        <v>6784785</v>
+        <v>6784603</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4331,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642666</v>
+        <v>121642267</v>
       </c>
       <c r="B36" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4343,30 +4359,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4374,10 +4395,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475136</v>
+        <v>475081</v>
       </c>
       <c r="R36" t="n">
-        <v>6784615</v>
+        <v>6784478</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4418,7 +4439,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4437,7 +4457,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642601</v>
+        <v>121643189</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4480,10 +4500,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475129</v>
+        <v>474585</v>
       </c>
       <c r="R37" t="n">
-        <v>6784603</v>
+        <v>6784789</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4543,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642751</v>
+        <v>121642803</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4559,26 +4579,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4586,10 +4611,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475056</v>
+        <v>474986</v>
       </c>
       <c r="R38" t="n">
-        <v>6784745</v>
+        <v>6784798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4630,7 +4655,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4649,10 +4673,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642482</v>
+        <v>121642942</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4665,31 +4689,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4697,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475111</v>
+        <v>474753</v>
       </c>
       <c r="R39" t="n">
-        <v>6784565</v>
+        <v>6784789</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,6 +4760,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4759,10 +4779,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121641324</v>
+        <v>121642751</v>
       </c>
       <c r="B40" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4775,31 +4795,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4807,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475075</v>
+        <v>475056</v>
       </c>
       <c r="R40" t="n">
-        <v>6784468</v>
+        <v>6784745</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4851,6 +4866,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4869,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642921</v>
+        <v>121642791</v>
       </c>
       <c r="B41" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4885,29 +4901,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4916,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474804</v>
+        <v>474995</v>
       </c>
       <c r="R41" t="n">
-        <v>6784818</v>
+        <v>6784797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4979,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121642742</v>
+        <v>121643023</v>
       </c>
       <c r="B42" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4995,31 +5007,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5027,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475084</v>
+        <v>474686</v>
       </c>
       <c r="R42" t="n">
-        <v>6784706</v>
+        <v>6784780</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5071,6 +5078,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5089,7 +5097,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121643203</v>
+        <v>121642987</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5132,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474542</v>
+        <v>474688</v>
       </c>
       <c r="R43" t="n">
-        <v>6784809</v>
+        <v>6784772</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,7 +5203,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642761</v>
+        <v>121642556</v>
       </c>
       <c r="B44" t="n">
         <v>57357</v>
@@ -5243,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475033</v>
+        <v>475112</v>
       </c>
       <c r="R44" t="n">
-        <v>6784752</v>
+        <v>6784581</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5305,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121643182</v>
+        <v>121642666</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5317,35 +5325,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5353,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474609</v>
+        <v>475136</v>
       </c>
       <c r="R45" t="n">
-        <v>6784770</v>
+        <v>6784615</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,6 +5400,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5415,10 +5419,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642718</v>
+        <v>121642729</v>
       </c>
       <c r="B46" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,35 +5435,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5467,10 +5462,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475154</v>
+        <v>475088</v>
       </c>
       <c r="R46" t="n">
-        <v>6784610</v>
+        <v>6784704</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5511,6 +5506,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5529,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642955</v>
+        <v>121642894</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5545,25 +5541,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474754</v>
+        <v>474806</v>
       </c>
       <c r="R47" t="n">
-        <v>6784810</v>
+        <v>6784787</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121643090</v>
+        <v>121643182</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5651,26 +5651,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5678,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474641</v>
+        <v>474609</v>
       </c>
       <c r="R48" t="n">
-        <v>6784795</v>
+        <v>6784770</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5722,7 +5727,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5741,10 +5745,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642894</v>
+        <v>121642506</v>
       </c>
       <c r="B49" t="n">
-        <v>90728</v>
+        <v>90748</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5757,24 +5761,28 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -5788,10 +5796,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>474806</v>
+        <v>475110</v>
       </c>
       <c r="R49" t="n">
-        <v>6784787</v>
+        <v>6784578</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5859,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642490</v>
+        <v>121642769</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5894,10 +5902,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475112</v>
+        <v>475021</v>
       </c>
       <c r="R50" t="n">
-        <v>6784571</v>
+        <v>6784769</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5957,7 +5965,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642493</v>
+        <v>121642260</v>
       </c>
       <c r="B51" t="n">
         <v>57357</v>
@@ -6005,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475116</v>
+        <v>475080</v>
       </c>
       <c r="R51" t="n">
-        <v>6784570</v>
+        <v>6784480</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,10 +6075,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642729</v>
+        <v>121642308</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6083,26 +6091,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6110,10 +6123,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475088</v>
+        <v>475127</v>
       </c>
       <c r="R52" t="n">
-        <v>6784704</v>
+        <v>6784476</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6154,7 +6167,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6173,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121643189</v>
+        <v>121642712</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,26 +6201,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6216,10 +6233,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474585</v>
+        <v>475147</v>
       </c>
       <c r="R53" t="n">
-        <v>6784789</v>
+        <v>6784617</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6260,7 +6277,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6279,10 +6295,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642267</v>
+        <v>121642869</v>
       </c>
       <c r="B54" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6295,31 +6311,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6327,10 +6338,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475081</v>
+        <v>474808</v>
       </c>
       <c r="R54" t="n">
-        <v>6784478</v>
+        <v>6784785</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6371,6 +6382,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6389,10 +6401,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642308</v>
+        <v>121643203</v>
       </c>
       <c r="B55" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6405,31 +6417,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6437,10 +6444,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475127</v>
+        <v>474542</v>
       </c>
       <c r="R55" t="n">
-        <v>6784476</v>
+        <v>6784809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6481,6 +6488,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6499,10 +6507,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121641316</v>
+        <v>121642847</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6515,31 +6523,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6547,10 +6550,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475090</v>
+        <v>474825</v>
       </c>
       <c r="R56" t="n">
-        <v>6784447</v>
+        <v>6784805</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6591,6 +6594,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6609,7 +6613,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642755</v>
+        <v>121642746</v>
       </c>
       <c r="B57" t="n">
         <v>78616</v>
@@ -6652,10 +6656,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475045</v>
+        <v>475079</v>
       </c>
       <c r="R57" t="n">
-        <v>6784754</v>
+        <v>6784712</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,10 +6719,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642648</v>
+        <v>121642755</v>
       </c>
       <c r="B58" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6731,31 +6735,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6763,10 +6762,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475130</v>
+        <v>475045</v>
       </c>
       <c r="R58" t="n">
-        <v>6784606</v>
+        <v>6784754</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6807,6 +6806,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6825,10 +6825,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642860</v>
+        <v>121642587</v>
       </c>
       <c r="B59" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6841,29 +6841,25 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -6872,10 +6868,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474820</v>
+        <v>475118</v>
       </c>
       <c r="R59" t="n">
-        <v>6784784</v>
+        <v>6784585</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6935,7 +6931,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121643037</v>
+        <v>121641324</v>
       </c>
       <c r="B60" t="n">
         <v>57357</v>
@@ -6983,10 +6979,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474681</v>
+        <v>475075</v>
       </c>
       <c r="R60" t="n">
-        <v>6784796</v>
+        <v>6784468</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7045,10 +7041,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121642587</v>
+        <v>121642742</v>
       </c>
       <c r="B61" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7061,26 +7057,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7088,10 +7089,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475118</v>
+        <v>475084</v>
       </c>
       <c r="R61" t="n">
-        <v>6784585</v>
+        <v>6784706</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7132,7 +7133,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807181</v>
+        <v>121807130</v>
       </c>
       <c r="B63" t="n">
         <v>78616</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475055</v>
+        <v>475111</v>
       </c>
       <c r="R63" t="n">
-        <v>6784636</v>
+        <v>6784416</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807130</v>
+        <v>121807181</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475111</v>
+        <v>475055</v>
       </c>
       <c r="R65" t="n">
-        <v>6784416</v>
+        <v>6784636</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121642976</v>
+        <v>121643103</v>
       </c>
       <c r="B2" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474731</v>
+        <v>474609</v>
       </c>
       <c r="R2" t="n">
-        <v>6784765</v>
+        <v>6784770</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642881</v>
+        <v>121642403</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474805</v>
+        <v>475125</v>
       </c>
       <c r="R3" t="n">
-        <v>6784786</v>
+        <v>6784471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642761</v>
+        <v>121642308</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475033</v>
+        <v>475127</v>
       </c>
       <c r="R4" t="n">
-        <v>6784752</v>
+        <v>6784476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642928</v>
+        <v>121642482</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,26 +1017,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1044,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474760</v>
+        <v>475111</v>
       </c>
       <c r="R5" t="n">
-        <v>6784798</v>
+        <v>6784565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642593</v>
+        <v>121642860</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1127,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1150,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475125</v>
+        <v>474820</v>
       </c>
       <c r="R6" t="n">
-        <v>6784604</v>
+        <v>6784784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1319,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642781</v>
+        <v>121641324</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1367,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475004</v>
+        <v>475075</v>
       </c>
       <c r="R8" t="n">
-        <v>6784792</v>
+        <v>6784468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642860</v>
+        <v>121642729</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,29 +1453,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1476,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474820</v>
+        <v>475088</v>
       </c>
       <c r="R9" t="n">
-        <v>6784784</v>
+        <v>6784704</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121641430</v>
+        <v>121642955</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,35 +1559,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475085</v>
+        <v>474754</v>
       </c>
       <c r="R10" t="n">
-        <v>6784456</v>
+        <v>6784810</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,6 +1630,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642300</v>
+        <v>121642660</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,31 +1665,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1701,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475106</v>
+        <v>475110</v>
       </c>
       <c r="R11" t="n">
-        <v>6784487</v>
+        <v>6784606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1763,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121643093</v>
+        <v>121642735</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1806,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474640</v>
+        <v>475086</v>
       </c>
       <c r="R12" t="n">
-        <v>6784795</v>
+        <v>6784704</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121642660</v>
+        <v>121643037</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,26 +1877,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475110</v>
+        <v>474681</v>
       </c>
       <c r="R13" t="n">
-        <v>6784606</v>
+        <v>6784796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1953,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1975,7 +1971,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121643049</v>
+        <v>121642603</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2018,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474659</v>
+        <v>475130</v>
       </c>
       <c r="R14" t="n">
-        <v>6784800</v>
+        <v>6784603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121642269</v>
+        <v>121642755</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,31 +2093,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475102</v>
+        <v>475045</v>
       </c>
       <c r="R15" t="n">
-        <v>6784483</v>
+        <v>6784754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,6 +2164,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642403</v>
+        <v>121642593</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,31 +2199,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2242,7 +2229,7 @@
         <v>475125</v>
       </c>
       <c r="R16" t="n">
-        <v>6784471</v>
+        <v>6784604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,6 +2270,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642499</v>
+        <v>121642648</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,26 +2305,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2344,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475105</v>
+        <v>475130</v>
       </c>
       <c r="R17" t="n">
-        <v>6784582</v>
+        <v>6784606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2381,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2407,7 +2399,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121641316</v>
+        <v>121642781</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2455,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475090</v>
+        <v>475004</v>
       </c>
       <c r="R18" t="n">
-        <v>6784447</v>
+        <v>6784792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121643037</v>
+        <v>121642601</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,31 +2525,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2565,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474681</v>
+        <v>475129</v>
       </c>
       <c r="R19" t="n">
-        <v>6784796</v>
+        <v>6784603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2609,6 +2596,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2627,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121643119</v>
+        <v>121641316</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,26 +2631,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2670,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474609</v>
+        <v>475090</v>
       </c>
       <c r="R20" t="n">
-        <v>6784770</v>
+        <v>6784447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2707,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2725,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642647</v>
+        <v>121642300</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,26 +2741,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2776,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475130</v>
+        <v>475106</v>
       </c>
       <c r="R21" t="n">
-        <v>6784606</v>
+        <v>6784487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,7 +2817,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2839,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642648</v>
+        <v>121642976</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,31 +2851,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2887,10 +2878,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475130</v>
+        <v>474731</v>
       </c>
       <c r="R22" t="n">
-        <v>6784606</v>
+        <v>6784765</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,6 +2922,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2949,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642718</v>
+        <v>121642499</v>
       </c>
       <c r="B23" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,35 +2957,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3001,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475154</v>
+        <v>475105</v>
       </c>
       <c r="R23" t="n">
-        <v>6784610</v>
+        <v>6784582</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,6 +3028,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3063,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642306</v>
+        <v>121642712</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,26 +3063,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3106,10 +3095,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475127</v>
+        <v>475147</v>
       </c>
       <c r="R24" t="n">
-        <v>6784476</v>
+        <v>6784617</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3150,7 +3139,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3169,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642735</v>
+        <v>121642260</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3185,26 +3173,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3212,10 +3205,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475086</v>
+        <v>475080</v>
       </c>
       <c r="R25" t="n">
-        <v>6784704</v>
+        <v>6784480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3249,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642673</v>
+        <v>121642761</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3291,26 +3283,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3318,10 +3315,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475137</v>
+        <v>475033</v>
       </c>
       <c r="R26" t="n">
-        <v>6784616</v>
+        <v>6784752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3362,7 +3359,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642921</v>
+        <v>121643093</v>
       </c>
       <c r="B27" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3397,29 +3393,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3428,10 +3420,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474804</v>
+        <v>474640</v>
       </c>
       <c r="R27" t="n">
-        <v>6784818</v>
+        <v>6784795</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,10 +3483,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642493</v>
+        <v>121642921</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,31 +3499,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3539,10 +3530,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475116</v>
+        <v>474804</v>
       </c>
       <c r="R28" t="n">
-        <v>6784570</v>
+        <v>6784818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3583,6 +3574,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3601,7 +3593,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642601</v>
+        <v>121642769</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475129</v>
+        <v>475021</v>
       </c>
       <c r="R29" t="n">
-        <v>6784603</v>
+        <v>6784769</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3707,7 +3699,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642985</v>
+        <v>121642673</v>
       </c>
       <c r="B30" t="n">
         <v>78616</v>
@@ -3750,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474703</v>
+        <v>475137</v>
       </c>
       <c r="R30" t="n">
-        <v>6784764</v>
+        <v>6784616</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3813,10 +3805,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642955</v>
+        <v>121642506</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>90748</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,25 +3821,33 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474754</v>
+        <v>475110</v>
       </c>
       <c r="R31" t="n">
-        <v>6784810</v>
+        <v>6784578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121643090</v>
+        <v>121642928</v>
       </c>
       <c r="B32" t="n">
         <v>78616</v>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474641</v>
+        <v>474760</v>
       </c>
       <c r="R32" t="n">
-        <v>6784795</v>
+        <v>6784798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4025,7 +4025,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121642490</v>
+        <v>121643049</v>
       </c>
       <c r="B33" t="n">
         <v>78616</v>
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475112</v>
+        <v>474659</v>
       </c>
       <c r="R33" t="n">
-        <v>6784571</v>
+        <v>6784800</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642482</v>
+        <v>121642493</v>
       </c>
       <c r="B34" t="n">
         <v>57357</v>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475111</v>
+        <v>475116</v>
       </c>
       <c r="R34" t="n">
-        <v>6784565</v>
+        <v>6784570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,10 +4241,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642603</v>
+        <v>121642881</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,26 +4257,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475130</v>
+        <v>474805</v>
       </c>
       <c r="R35" t="n">
-        <v>6784603</v>
+        <v>6784786</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4328,7 +4333,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4347,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642267</v>
+        <v>121642666</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4359,35 +4363,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4395,10 +4394,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475081</v>
+        <v>475136</v>
       </c>
       <c r="R36" t="n">
-        <v>6784478</v>
+        <v>6784615</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4439,6 +4438,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121643189</v>
+        <v>121643023</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474585</v>
+        <v>474686</v>
       </c>
       <c r="R37" t="n">
-        <v>6784789</v>
+        <v>6784780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642803</v>
+        <v>121642869</v>
       </c>
       <c r="B38" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,31 +4579,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474986</v>
+        <v>474808</v>
       </c>
       <c r="R38" t="n">
-        <v>6784798</v>
+        <v>6784785</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4655,6 +4650,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4673,7 +4669,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642942</v>
+        <v>121643203</v>
       </c>
       <c r="B39" t="n">
         <v>78616</v>
@@ -4716,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474753</v>
+        <v>474542</v>
       </c>
       <c r="R39" t="n">
-        <v>6784789</v>
+        <v>6784809</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4779,7 +4775,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642751</v>
+        <v>121642490</v>
       </c>
       <c r="B40" t="n">
         <v>78616</v>
@@ -4822,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475056</v>
+        <v>475112</v>
       </c>
       <c r="R40" t="n">
-        <v>6784745</v>
+        <v>6784571</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,10 +4881,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642791</v>
+        <v>121642556</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,26 +4897,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4928,10 +4929,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474995</v>
+        <v>475112</v>
       </c>
       <c r="R41" t="n">
-        <v>6784797</v>
+        <v>6784581</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4973,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121643023</v>
+        <v>121643182</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,26 +5007,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5034,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474686</v>
+        <v>474609</v>
       </c>
       <c r="R42" t="n">
-        <v>6784780</v>
+        <v>6784770</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5078,7 +5083,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5097,7 +5101,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121642987</v>
+        <v>121642847</v>
       </c>
       <c r="B43" t="n">
         <v>78616</v>
@@ -5140,10 +5144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474688</v>
+        <v>474825</v>
       </c>
       <c r="R43" t="n">
-        <v>6784772</v>
+        <v>6784805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642556</v>
+        <v>121642746</v>
       </c>
       <c r="B44" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,31 +5223,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5250,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475112</v>
+        <v>475079</v>
       </c>
       <c r="R44" t="n">
-        <v>6784581</v>
+        <v>6784712</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,6 +5294,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121642666</v>
+        <v>121643090</v>
       </c>
       <c r="B45" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,25 +5325,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475136</v>
+        <v>474641</v>
       </c>
       <c r="R45" t="n">
-        <v>6784615</v>
+        <v>6784795</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642729</v>
+        <v>121642742</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,26 +5435,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5462,10 +5467,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475088</v>
+        <v>475084</v>
       </c>
       <c r="R46" t="n">
-        <v>6784704</v>
+        <v>6784706</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5506,7 +5511,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5525,10 +5529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642894</v>
+        <v>121642803</v>
       </c>
       <c r="B47" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,30 +5545,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5572,10 +5577,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474806</v>
+        <v>474986</v>
       </c>
       <c r="R47" t="n">
-        <v>6784787</v>
+        <v>6784798</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,7 +5621,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5635,10 +5639,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121643182</v>
+        <v>121642942</v>
       </c>
       <c r="B48" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5651,31 +5655,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5683,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474609</v>
+        <v>474753</v>
       </c>
       <c r="R48" t="n">
-        <v>6784770</v>
+        <v>6784789</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5727,6 +5726,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642506</v>
+        <v>121642647</v>
       </c>
       <c r="B49" t="n">
-        <v>90748</v>
+        <v>78616</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5761,33 +5761,25 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5796,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475110</v>
+        <v>475130</v>
       </c>
       <c r="R49" t="n">
-        <v>6784578</v>
+        <v>6784606</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5859,7 +5851,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642769</v>
+        <v>121642306</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5902,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475021</v>
+        <v>475127</v>
       </c>
       <c r="R50" t="n">
-        <v>6784769</v>
+        <v>6784476</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5965,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642260</v>
+        <v>121642791</v>
       </c>
       <c r="B51" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5981,31 +5973,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6013,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475080</v>
+        <v>474995</v>
       </c>
       <c r="R51" t="n">
-        <v>6784480</v>
+        <v>6784797</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6057,6 +6044,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6075,10 +6063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642308</v>
+        <v>121642718</v>
       </c>
       <c r="B52" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6091,29 +6079,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6123,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475127</v>
+        <v>475154</v>
       </c>
       <c r="R52" t="n">
-        <v>6784476</v>
+        <v>6784610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6185,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642712</v>
+        <v>121642587</v>
       </c>
       <c r="B53" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6201,31 +6193,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6233,10 +6220,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475147</v>
+        <v>475118</v>
       </c>
       <c r="R53" t="n">
-        <v>6784617</v>
+        <v>6784585</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6277,6 +6264,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6295,10 +6283,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642869</v>
+        <v>121642267</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6311,26 +6299,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6338,10 +6331,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474808</v>
+        <v>475081</v>
       </c>
       <c r="R54" t="n">
-        <v>6784785</v>
+        <v>6784478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6382,7 +6375,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6401,10 +6393,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121643203</v>
+        <v>121642269</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6417,26 +6409,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6444,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474542</v>
+        <v>475102</v>
       </c>
       <c r="R55" t="n">
-        <v>6784809</v>
+        <v>6784483</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6485,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6507,7 +6503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642847</v>
+        <v>121642751</v>
       </c>
       <c r="B56" t="n">
         <v>78616</v>
@@ -6550,10 +6546,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474825</v>
+        <v>475056</v>
       </c>
       <c r="R56" t="n">
-        <v>6784805</v>
+        <v>6784745</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6613,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642746</v>
+        <v>121641430</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6629,26 +6625,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6656,10 +6661,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475079</v>
+        <v>475085</v>
       </c>
       <c r="R57" t="n">
-        <v>6784712</v>
+        <v>6784456</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6700,7 +6705,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6719,7 +6723,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642755</v>
+        <v>121642987</v>
       </c>
       <c r="B58" t="n">
         <v>78616</v>
@@ -6762,10 +6766,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475045</v>
+        <v>474688</v>
       </c>
       <c r="R58" t="n">
-        <v>6784754</v>
+        <v>6784772</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6825,7 +6829,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642587</v>
+        <v>121642985</v>
       </c>
       <c r="B59" t="n">
         <v>78616</v>
@@ -6868,10 +6872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475118</v>
+        <v>474703</v>
       </c>
       <c r="R59" t="n">
-        <v>6784585</v>
+        <v>6784764</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6931,10 +6935,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121641324</v>
+        <v>121643189</v>
       </c>
       <c r="B60" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6947,31 +6951,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6979,10 +6978,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475075</v>
+        <v>474585</v>
       </c>
       <c r="R60" t="n">
-        <v>6784468</v>
+        <v>6784789</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7023,6 +7022,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7041,10 +7041,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121642742</v>
+        <v>121642894</v>
       </c>
       <c r="B61" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7057,31 +7057,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7089,10 +7088,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475084</v>
+        <v>474806</v>
       </c>
       <c r="R61" t="n">
-        <v>6784706</v>
+        <v>6784787</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7133,6 +7132,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121643103</v>
+        <v>121642955</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474609</v>
+        <v>474754</v>
       </c>
       <c r="R2" t="n">
-        <v>6784770</v>
+        <v>6784810</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642403</v>
+        <v>121642267</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475125</v>
+        <v>475081</v>
       </c>
       <c r="R3" t="n">
-        <v>6784471</v>
+        <v>6784478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642308</v>
+        <v>121642781</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475127</v>
+        <v>475004</v>
       </c>
       <c r="R4" t="n">
-        <v>6784476</v>
+        <v>6784792</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642482</v>
+        <v>121642506</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90748</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,31 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475111</v>
+        <v>475110</v>
       </c>
       <c r="R5" t="n">
-        <v>6784565</v>
+        <v>6784578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642860</v>
+        <v>121642928</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,29 +1131,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474820</v>
+        <v>474760</v>
       </c>
       <c r="R6" t="n">
-        <v>6784784</v>
+        <v>6784798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642964</v>
+        <v>121643093</v>
       </c>
       <c r="B7" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474746</v>
+        <v>474640</v>
       </c>
       <c r="R7" t="n">
-        <v>6784772</v>
+        <v>6784795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121641324</v>
+        <v>121642499</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,31 +1343,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475075</v>
+        <v>475105</v>
       </c>
       <c r="R8" t="n">
-        <v>6784468</v>
+        <v>6784582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,6 +1414,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1437,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642729</v>
+        <v>121642712</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,26 +1449,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1480,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475088</v>
+        <v>475147</v>
       </c>
       <c r="R9" t="n">
-        <v>6784704</v>
+        <v>6784617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1525,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642955</v>
+        <v>121642894</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1559,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474754</v>
+        <v>474806</v>
       </c>
       <c r="R10" t="n">
-        <v>6784810</v>
+        <v>6784787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642660</v>
+        <v>121642482</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,26 +1669,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1692,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475110</v>
+        <v>475111</v>
       </c>
       <c r="R11" t="n">
-        <v>6784606</v>
+        <v>6784565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1745,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1755,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642735</v>
+        <v>121642601</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1798,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475086</v>
+        <v>475129</v>
       </c>
       <c r="R12" t="n">
-        <v>6784704</v>
+        <v>6784603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121643037</v>
+        <v>121643119</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,31 +1885,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474681</v>
+        <v>474609</v>
       </c>
       <c r="R13" t="n">
-        <v>6784796</v>
+        <v>6784770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,6 +1956,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1971,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121642603</v>
+        <v>121642650</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2017,7 +2021,7 @@
         <v>475130</v>
       </c>
       <c r="R14" t="n">
-        <v>6784603</v>
+        <v>6784606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121642755</v>
+        <v>121642735</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2120,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475045</v>
+        <v>475086</v>
       </c>
       <c r="R15" t="n">
-        <v>6784754</v>
+        <v>6784704</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642593</v>
+        <v>121642718</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,26 +2203,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2226,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475125</v>
+        <v>475154</v>
       </c>
       <c r="R16" t="n">
-        <v>6784604</v>
+        <v>6784610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2283,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2289,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642648</v>
+        <v>121641430</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,29 +2317,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2337,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475130</v>
+        <v>475085</v>
       </c>
       <c r="R17" t="n">
-        <v>6784606</v>
+        <v>6784456</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,7 +2415,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642781</v>
+        <v>121642308</v>
       </c>
       <c r="B18" t="n">
         <v>57357</v>
@@ -2447,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475004</v>
+        <v>475127</v>
       </c>
       <c r="R18" t="n">
-        <v>6784792</v>
+        <v>6784476</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642601</v>
+        <v>121642269</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2525,26 +2541,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2552,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475129</v>
+        <v>475102</v>
       </c>
       <c r="R19" t="n">
-        <v>6784603</v>
+        <v>6784483</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2617,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2615,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121641316</v>
+        <v>121642769</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2631,31 +2651,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2663,10 +2678,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475090</v>
+        <v>475021</v>
       </c>
       <c r="R20" t="n">
-        <v>6784447</v>
+        <v>6784769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,6 +2722,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2725,10 +2741,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642300</v>
+        <v>121642673</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2741,31 +2757,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2773,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475106</v>
+        <v>475137</v>
       </c>
       <c r="R21" t="n">
-        <v>6784487</v>
+        <v>6784616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,6 +2828,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2835,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642976</v>
+        <v>121642660</v>
       </c>
       <c r="B22" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,21 +2863,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2878,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474731</v>
+        <v>475110</v>
       </c>
       <c r="R22" t="n">
-        <v>6784765</v>
+        <v>6784606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642499</v>
+        <v>121642593</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -2984,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475105</v>
+        <v>475125</v>
       </c>
       <c r="R23" t="n">
-        <v>6784582</v>
+        <v>6784604</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642712</v>
+        <v>121642881</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3095,10 +3107,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>475147</v>
+        <v>474805</v>
       </c>
       <c r="R24" t="n">
-        <v>6784617</v>
+        <v>6784786</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642260</v>
+        <v>121642869</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,31 +3185,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3205,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475080</v>
+        <v>474808</v>
       </c>
       <c r="R25" t="n">
-        <v>6784480</v>
+        <v>6784785</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,6 +3256,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3267,10 +3275,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642761</v>
+        <v>121643203</v>
       </c>
       <c r="B26" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,31 +3291,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3315,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475033</v>
+        <v>474542</v>
       </c>
       <c r="R26" t="n">
-        <v>6784752</v>
+        <v>6784809</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,6 +3362,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3377,7 +3381,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121643093</v>
+        <v>121642490</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3420,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474640</v>
+        <v>475112</v>
       </c>
       <c r="R27" t="n">
-        <v>6784795</v>
+        <v>6784571</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3483,10 +3487,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642921</v>
+        <v>121642666</v>
       </c>
       <c r="B28" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,33 +3499,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474804</v>
+        <v>475136</v>
       </c>
       <c r="R28" t="n">
-        <v>6784818</v>
+        <v>6784615</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3593,7 +3593,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642769</v>
+        <v>121642755</v>
       </c>
       <c r="B29" t="n">
         <v>78616</v>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475021</v>
+        <v>475045</v>
       </c>
       <c r="R29" t="n">
-        <v>6784769</v>
+        <v>6784754</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642673</v>
+        <v>121642260</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,26 +3715,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3742,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475137</v>
+        <v>475080</v>
       </c>
       <c r="R30" t="n">
-        <v>6784616</v>
+        <v>6784480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3786,7 +3791,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3805,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642506</v>
+        <v>121642761</v>
       </c>
       <c r="B31" t="n">
-        <v>90748</v>
+        <v>57357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,34 +3825,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3856,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475110</v>
+        <v>475033</v>
       </c>
       <c r="R31" t="n">
-        <v>6784578</v>
+        <v>6784752</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3900,7 +3901,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121642928</v>
+        <v>121642300</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3935,26 +3935,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3962,10 +3967,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474760</v>
+        <v>475106</v>
       </c>
       <c r="R32" t="n">
-        <v>6784798</v>
+        <v>6784487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4006,7 +4011,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4025,10 +4029,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121643049</v>
+        <v>121642964</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4041,21 +4045,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4068,10 +4072,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474659</v>
+        <v>474746</v>
       </c>
       <c r="R33" t="n">
-        <v>6784800</v>
+        <v>6784772</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,10 +4135,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642493</v>
+        <v>121642751</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4147,31 +4151,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4179,10 +4178,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475116</v>
+        <v>475056</v>
       </c>
       <c r="R34" t="n">
-        <v>6784570</v>
+        <v>6784745</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4223,6 +4222,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642881</v>
+        <v>121642742</v>
       </c>
       <c r="B35" t="n">
         <v>57357</v>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>474805</v>
+        <v>475084</v>
       </c>
       <c r="R35" t="n">
-        <v>6784786</v>
+        <v>6784706</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642666</v>
+        <v>121642556</v>
       </c>
       <c r="B36" t="n">
-        <v>90693</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,30 +4363,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4394,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475136</v>
+        <v>475112</v>
       </c>
       <c r="R36" t="n">
-        <v>6784615</v>
+        <v>6784581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4438,7 +4443,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4457,7 +4461,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121643023</v>
+        <v>121643049</v>
       </c>
       <c r="B37" t="n">
         <v>78616</v>
@@ -4500,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474686</v>
+        <v>474659</v>
       </c>
       <c r="R37" t="n">
-        <v>6784780</v>
+        <v>6784800</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,10 +4567,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642869</v>
+        <v>121642803</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,26 +4583,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4606,10 +4615,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474808</v>
+        <v>474986</v>
       </c>
       <c r="R38" t="n">
-        <v>6784785</v>
+        <v>6784798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4650,7 +4659,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4669,10 +4677,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121643203</v>
+        <v>121642493</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,26 +4693,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4712,10 +4725,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474542</v>
+        <v>475116</v>
       </c>
       <c r="R39" t="n">
-        <v>6784809</v>
+        <v>6784570</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4756,7 +4769,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4775,7 +4787,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642490</v>
+        <v>121642942</v>
       </c>
       <c r="B40" t="n">
         <v>78616</v>
@@ -4818,10 +4830,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>475112</v>
+        <v>474753</v>
       </c>
       <c r="R40" t="n">
-        <v>6784571</v>
+        <v>6784789</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4881,10 +4893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642556</v>
+        <v>121642603</v>
       </c>
       <c r="B41" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,31 +4909,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4929,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475112</v>
+        <v>475130</v>
       </c>
       <c r="R41" t="n">
-        <v>6784581</v>
+        <v>6784603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4973,6 +4980,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +4999,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121643182</v>
+        <v>121642791</v>
       </c>
       <c r="B42" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,31 +5015,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5042,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474609</v>
+        <v>474995</v>
       </c>
       <c r="R42" t="n">
-        <v>6784770</v>
+        <v>6784797</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5083,6 +5086,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5101,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121642847</v>
+        <v>121642403</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5117,26 +5121,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5144,10 +5153,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474825</v>
+        <v>475125</v>
       </c>
       <c r="R43" t="n">
-        <v>6784805</v>
+        <v>6784471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5188,7 +5197,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5207,7 +5215,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642746</v>
+        <v>121643023</v>
       </c>
       <c r="B44" t="n">
         <v>78616</v>
@@ -5250,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475079</v>
+        <v>474686</v>
       </c>
       <c r="R44" t="n">
-        <v>6784712</v>
+        <v>6784780</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5313,7 +5321,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121643090</v>
+        <v>121642985</v>
       </c>
       <c r="B45" t="n">
         <v>78616</v>
@@ -5356,10 +5364,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474641</v>
+        <v>474703</v>
       </c>
       <c r="R45" t="n">
-        <v>6784795</v>
+        <v>6784764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5419,10 +5427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642742</v>
+        <v>121642987</v>
       </c>
       <c r="B46" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,31 +5443,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5467,10 +5470,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475084</v>
+        <v>474688</v>
       </c>
       <c r="R46" t="n">
-        <v>6784706</v>
+        <v>6784772</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5511,6 +5514,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5529,7 +5533,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642803</v>
+        <v>121642648</v>
       </c>
       <c r="B47" t="n">
         <v>57357</v>
@@ -5577,10 +5581,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474986</v>
+        <v>475130</v>
       </c>
       <c r="R47" t="n">
-        <v>6784798</v>
+        <v>6784606</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121642942</v>
+        <v>121641316</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5655,26 +5659,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5682,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>474753</v>
+        <v>475090</v>
       </c>
       <c r="R48" t="n">
-        <v>6784789</v>
+        <v>6784447</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5726,7 +5735,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5745,7 +5753,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642647</v>
+        <v>121642746</v>
       </c>
       <c r="B49" t="n">
         <v>78616</v>
@@ -5788,10 +5796,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475130</v>
+        <v>475079</v>
       </c>
       <c r="R49" t="n">
-        <v>6784606</v>
+        <v>6784712</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5859,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642306</v>
+        <v>121642847</v>
       </c>
       <c r="B50" t="n">
         <v>78616</v>
@@ -5894,10 +5902,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475127</v>
+        <v>474825</v>
       </c>
       <c r="R50" t="n">
-        <v>6784476</v>
+        <v>6784805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5957,7 +5965,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642791</v>
+        <v>121642306</v>
       </c>
       <c r="B51" t="n">
         <v>78616</v>
@@ -6000,10 +6008,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474995</v>
+        <v>475127</v>
       </c>
       <c r="R51" t="n">
-        <v>6784797</v>
+        <v>6784476</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6063,10 +6071,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642718</v>
+        <v>121642587</v>
       </c>
       <c r="B52" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6079,35 +6087,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6115,10 +6114,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475154</v>
+        <v>475118</v>
       </c>
       <c r="R52" t="n">
-        <v>6784610</v>
+        <v>6784585</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6159,6 +6158,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6177,10 +6177,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642587</v>
+        <v>121641324</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6193,26 +6193,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6220,10 +6225,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475118</v>
+        <v>475075</v>
       </c>
       <c r="R53" t="n">
-        <v>6784585</v>
+        <v>6784468</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6264,7 +6269,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6283,7 +6287,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642267</v>
+        <v>121643182</v>
       </c>
       <c r="B54" t="n">
         <v>57357</v>
@@ -6331,10 +6335,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475081</v>
+        <v>474609</v>
       </c>
       <c r="R54" t="n">
-        <v>6784478</v>
+        <v>6784770</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6393,10 +6397,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642269</v>
+        <v>121643189</v>
       </c>
       <c r="B55" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6409,31 +6413,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6441,10 +6440,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475102</v>
+        <v>474585</v>
       </c>
       <c r="R55" t="n">
-        <v>6784483</v>
+        <v>6784789</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6485,6 +6484,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642751</v>
+        <v>121643090</v>
       </c>
       <c r="B56" t="n">
         <v>78616</v>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475056</v>
+        <v>474641</v>
       </c>
       <c r="R56" t="n">
-        <v>6784745</v>
+        <v>6784795</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121641430</v>
+        <v>121642729</v>
       </c>
       <c r="B57" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6625,35 +6625,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6661,10 +6652,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475085</v>
+        <v>475088</v>
       </c>
       <c r="R57" t="n">
-        <v>6784456</v>
+        <v>6784704</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6705,6 +6696,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6723,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642987</v>
+        <v>121642976</v>
       </c>
       <c r="B58" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6739,21 +6731,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6766,10 +6758,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474688</v>
+        <v>474731</v>
       </c>
       <c r="R58" t="n">
-        <v>6784772</v>
+        <v>6784765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6829,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642985</v>
+        <v>121642921</v>
       </c>
       <c r="B59" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6845,25 +6837,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -6872,10 +6868,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474703</v>
+        <v>474804</v>
       </c>
       <c r="R59" t="n">
-        <v>6784764</v>
+        <v>6784818</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6935,10 +6931,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121643189</v>
+        <v>121642860</v>
       </c>
       <c r="B60" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6951,25 +6947,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474585</v>
+        <v>474820</v>
       </c>
       <c r="R60" t="n">
-        <v>6784789</v>
+        <v>6784784</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7041,10 +7041,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121642894</v>
+        <v>121643037</v>
       </c>
       <c r="B61" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7057,30 +7057,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7088,10 +7089,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474806</v>
+        <v>474681</v>
       </c>
       <c r="R61" t="n">
-        <v>6784787</v>
+        <v>6784796</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7132,7 +7133,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807130</v>
+        <v>121807181</v>
       </c>
       <c r="B63" t="n">
         <v>78616</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475111</v>
+        <v>475055</v>
       </c>
       <c r="R63" t="n">
-        <v>6784416</v>
+        <v>6784636</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807149</v>
+        <v>121807130</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475105</v>
+        <v>475111</v>
       </c>
       <c r="R64" t="n">
-        <v>6784482</v>
+        <v>6784416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807181</v>
+        <v>121807149</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475055</v>
+        <v>475105</v>
       </c>
       <c r="R65" t="n">
-        <v>6784636</v>
+        <v>6784482</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -4461,10 +4461,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121643049</v>
+        <v>121642803</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4477,26 +4477,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474659</v>
+        <v>474986</v>
       </c>
       <c r="R37" t="n">
-        <v>6784800</v>
+        <v>6784798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4548,7 +4553,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4567,7 +4571,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642803</v>
+        <v>121642493</v>
       </c>
       <c r="B38" t="n">
         <v>57357</v>
@@ -4615,10 +4619,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>474986</v>
+        <v>475116</v>
       </c>
       <c r="R38" t="n">
-        <v>6784798</v>
+        <v>6784570</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4677,10 +4681,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121642493</v>
+        <v>121643049</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4693,31 +4697,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4725,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475116</v>
+        <v>474659</v>
       </c>
       <c r="R39" t="n">
-        <v>6784570</v>
+        <v>6784800</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,6 +4768,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642847</v>
+        <v>121641324</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5875,26 +5875,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5902,10 +5907,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>474825</v>
+        <v>475075</v>
       </c>
       <c r="R50" t="n">
-        <v>6784805</v>
+        <v>6784468</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5946,7 +5951,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5965,10 +5969,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121642306</v>
+        <v>121643182</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5981,26 +5985,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6008,10 +6017,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>475127</v>
+        <v>474609</v>
       </c>
       <c r="R51" t="n">
-        <v>6784476</v>
+        <v>6784770</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6052,7 +6061,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6071,7 +6079,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642587</v>
+        <v>121642847</v>
       </c>
       <c r="B52" t="n">
         <v>78616</v>
@@ -6114,10 +6122,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475118</v>
+        <v>474825</v>
       </c>
       <c r="R52" t="n">
-        <v>6784585</v>
+        <v>6784805</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6177,10 +6185,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121641324</v>
+        <v>121642306</v>
       </c>
       <c r="B53" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6193,31 +6201,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6225,10 +6228,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475075</v>
+        <v>475127</v>
       </c>
       <c r="R53" t="n">
-        <v>6784468</v>
+        <v>6784476</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6269,6 +6272,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6287,10 +6291,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121643182</v>
+        <v>121642587</v>
       </c>
       <c r="B54" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6303,31 +6307,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6335,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474609</v>
+        <v>475118</v>
       </c>
       <c r="R54" t="n">
-        <v>6784770</v>
+        <v>6784585</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6379,6 +6378,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6609,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642729</v>
+        <v>121642976</v>
       </c>
       <c r="B57" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6625,21 +6625,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>475088</v>
+        <v>474731</v>
       </c>
       <c r="R57" t="n">
-        <v>6784704</v>
+        <v>6784765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,10 +6715,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642976</v>
+        <v>121642729</v>
       </c>
       <c r="B58" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6731,21 +6731,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>474731</v>
+        <v>475088</v>
       </c>
       <c r="R58" t="n">
-        <v>6784765</v>
+        <v>6784704</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121642955</v>
+        <v>121642729</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474754</v>
+        <v>475088</v>
       </c>
       <c r="R2" t="n">
-        <v>6784810</v>
+        <v>6784704</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642267</v>
+        <v>121642673</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475081</v>
+        <v>475137</v>
       </c>
       <c r="R3" t="n">
-        <v>6784478</v>
+        <v>6784616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642781</v>
+        <v>121643037</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -939,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475004</v>
+        <v>474681</v>
       </c>
       <c r="R4" t="n">
-        <v>6784792</v>
+        <v>6784796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642506</v>
+        <v>121642260</v>
       </c>
       <c r="B5" t="n">
-        <v>90748</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1013,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475110</v>
+        <v>475080</v>
       </c>
       <c r="R5" t="n">
-        <v>6784578</v>
+        <v>6784480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642928</v>
+        <v>121642300</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,26 +1123,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474760</v>
+        <v>475106</v>
       </c>
       <c r="R6" t="n">
-        <v>6784798</v>
+        <v>6784487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1199,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121643093</v>
+        <v>121642921</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1233,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474640</v>
+        <v>474804</v>
       </c>
       <c r="R7" t="n">
-        <v>6784795</v>
+        <v>6784818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642499</v>
+        <v>121642964</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>78650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475105</v>
+        <v>474746</v>
       </c>
       <c r="R8" t="n">
-        <v>6784582</v>
+        <v>6784772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642712</v>
+        <v>121643103</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,31 +1449,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475147</v>
+        <v>474609</v>
       </c>
       <c r="R9" t="n">
-        <v>6784617</v>
+        <v>6784770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1520,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642894</v>
+        <v>121642666</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,33 +1551,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1590,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474806</v>
+        <v>475136</v>
       </c>
       <c r="R10" t="n">
-        <v>6784787</v>
+        <v>6784615</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1645,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642482</v>
+        <v>121642267</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1701,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475111</v>
+        <v>475081</v>
       </c>
       <c r="R11" t="n">
-        <v>6784565</v>
+        <v>6784478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121642601</v>
+        <v>121643023</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1806,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475129</v>
+        <v>474686</v>
       </c>
       <c r="R12" t="n">
-        <v>6784603</v>
+        <v>6784780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121643119</v>
+        <v>121642603</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1912,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474609</v>
+        <v>475130</v>
       </c>
       <c r="R13" t="n">
-        <v>6784770</v>
+        <v>6784603</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121642650</v>
+        <v>121642803</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,26 +1983,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475130</v>
+        <v>474986</v>
       </c>
       <c r="R14" t="n">
-        <v>6784606</v>
+        <v>6784798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,7 +2059,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121642735</v>
+        <v>121642791</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2124,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475086</v>
+        <v>474995</v>
       </c>
       <c r="R15" t="n">
-        <v>6784704</v>
+        <v>6784797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642718</v>
+        <v>121642751</v>
       </c>
       <c r="B16" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,35 +2199,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2239,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475154</v>
+        <v>475056</v>
       </c>
       <c r="R16" t="n">
-        <v>6784610</v>
+        <v>6784745</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,6 +2270,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121641430</v>
+        <v>121642660</v>
       </c>
       <c r="B17" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,35 +2305,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2353,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475085</v>
+        <v>475110</v>
       </c>
       <c r="R17" t="n">
-        <v>6784456</v>
+        <v>6784606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,6 +2376,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2415,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642308</v>
+        <v>121642987</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2431,31 +2411,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2463,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475127</v>
+        <v>474688</v>
       </c>
       <c r="R18" t="n">
-        <v>6784476</v>
+        <v>6784772</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,6 +2482,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2525,10 +2501,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642269</v>
+        <v>121642587</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,31 +2517,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2573,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475102</v>
+        <v>475118</v>
       </c>
       <c r="R19" t="n">
-        <v>6784483</v>
+        <v>6784585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2617,6 +2588,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2635,10 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121642769</v>
+        <v>121642761</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2651,26 +2623,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2678,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475021</v>
+        <v>475033</v>
       </c>
       <c r="R20" t="n">
-        <v>6784769</v>
+        <v>6784752</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,7 +2699,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2741,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642673</v>
+        <v>121642648</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2757,26 +2733,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2784,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475137</v>
+        <v>475130</v>
       </c>
       <c r="R21" t="n">
-        <v>6784616</v>
+        <v>6784606</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2809,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2847,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642660</v>
+        <v>121642482</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2863,26 +2843,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475110</v>
+        <v>475111</v>
       </c>
       <c r="R22" t="n">
-        <v>6784606</v>
+        <v>6784565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,7 +2919,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2953,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642593</v>
+        <v>121642718</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,26 +2953,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2996,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475125</v>
+        <v>475154</v>
       </c>
       <c r="R23" t="n">
-        <v>6784604</v>
+        <v>6784610</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3033,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3059,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642881</v>
+        <v>121642976</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3075,31 +3067,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3107,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474805</v>
+        <v>474731</v>
       </c>
       <c r="R24" t="n">
-        <v>6784786</v>
+        <v>6784765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3151,6 +3138,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3169,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642869</v>
+        <v>121641316</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3185,26 +3173,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3212,10 +3205,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474808</v>
+        <v>475090</v>
       </c>
       <c r="R25" t="n">
-        <v>6784785</v>
+        <v>6784447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3249,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3267,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121643203</v>
+        <v>121642601</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3318,10 +3310,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474542</v>
+        <v>475129</v>
       </c>
       <c r="R26" t="n">
-        <v>6784809</v>
+        <v>6784603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3381,7 +3373,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642490</v>
+        <v>121642769</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3424,10 +3416,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475112</v>
+        <v>475021</v>
       </c>
       <c r="R27" t="n">
-        <v>6784571</v>
+        <v>6784769</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642666</v>
+        <v>121642928</v>
       </c>
       <c r="B28" t="n">
-        <v>90693</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3499,25 +3491,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3530,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>475136</v>
+        <v>474760</v>
       </c>
       <c r="R28" t="n">
-        <v>6784615</v>
+        <v>6784798</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3593,10 +3585,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642755</v>
+        <v>121642860</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3609,25 +3601,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3636,10 +3632,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>475045</v>
+        <v>474820</v>
       </c>
       <c r="R29" t="n">
-        <v>6784754</v>
+        <v>6784784</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,10 +3695,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121642260</v>
+        <v>121643090</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,31 +3711,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3747,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475080</v>
+        <v>474641</v>
       </c>
       <c r="R30" t="n">
-        <v>6784480</v>
+        <v>6784795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,6 +3782,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3809,10 +3801,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642761</v>
+        <v>121642306</v>
       </c>
       <c r="B31" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3825,31 +3817,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3857,10 +3844,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475033</v>
+        <v>475127</v>
       </c>
       <c r="R31" t="n">
-        <v>6784752</v>
+        <v>6784476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3901,6 +3888,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3919,7 +3907,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121642300</v>
+        <v>121641324</v>
       </c>
       <c r="B32" t="n">
         <v>57357</v>
@@ -3967,10 +3955,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475106</v>
+        <v>475075</v>
       </c>
       <c r="R32" t="n">
-        <v>6784487</v>
+        <v>6784468</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121642964</v>
+        <v>121643182</v>
       </c>
       <c r="B33" t="n">
-        <v>78650</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,26 +4033,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4072,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474746</v>
+        <v>474609</v>
       </c>
       <c r="R33" t="n">
-        <v>6784772</v>
+        <v>6784770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,7 +4109,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4135,7 +4127,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642751</v>
+        <v>121642955</v>
       </c>
       <c r="B34" t="n">
         <v>78616</v>
@@ -4178,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475056</v>
+        <v>474754</v>
       </c>
       <c r="R34" t="n">
-        <v>6784745</v>
+        <v>6784810</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642742</v>
+        <v>121642650</v>
       </c>
       <c r="B35" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4257,31 +4249,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4289,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475084</v>
+        <v>475130</v>
       </c>
       <c r="R35" t="n">
-        <v>6784706</v>
+        <v>6784606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4333,6 +4320,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4351,10 +4339,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642556</v>
+        <v>121642735</v>
       </c>
       <c r="B36" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4367,31 +4355,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4399,10 +4382,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475112</v>
+        <v>475086</v>
       </c>
       <c r="R36" t="n">
-        <v>6784581</v>
+        <v>6784704</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,6 +4426,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4461,7 +4445,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642803</v>
+        <v>121642493</v>
       </c>
       <c r="B37" t="n">
         <v>57357</v>
@@ -4509,10 +4493,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>474986</v>
+        <v>475116</v>
       </c>
       <c r="R37" t="n">
-        <v>6784798</v>
+        <v>6784570</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4571,7 +4555,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642493</v>
+        <v>121642781</v>
       </c>
       <c r="B38" t="n">
         <v>57357</v>
@@ -4619,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475116</v>
+        <v>475004</v>
       </c>
       <c r="R38" t="n">
-        <v>6784570</v>
+        <v>6784792</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4681,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121643049</v>
+        <v>121641430</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4697,26 +4681,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4724,10 +4717,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>474659</v>
+        <v>475085</v>
       </c>
       <c r="R39" t="n">
-        <v>6784800</v>
+        <v>6784456</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,7 +4761,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4893,7 +4885,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642603</v>
+        <v>121642847</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -4936,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475130</v>
+        <v>474825</v>
       </c>
       <c r="R41" t="n">
-        <v>6784603</v>
+        <v>6784805</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4999,7 +4991,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121642791</v>
+        <v>121642985</v>
       </c>
       <c r="B42" t="n">
         <v>78616</v>
@@ -5042,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474995</v>
+        <v>474703</v>
       </c>
       <c r="R42" t="n">
-        <v>6784797</v>
+        <v>6784764</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121642403</v>
+        <v>121643203</v>
       </c>
       <c r="B43" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5121,31 +5113,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5153,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>475125</v>
+        <v>474542</v>
       </c>
       <c r="R43" t="n">
-        <v>6784471</v>
+        <v>6784809</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5197,6 +5184,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5215,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121643023</v>
+        <v>121642269</v>
       </c>
       <c r="B44" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5231,26 +5219,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5258,10 +5251,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>474686</v>
+        <v>475102</v>
       </c>
       <c r="R44" t="n">
-        <v>6784780</v>
+        <v>6784483</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5295,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5321,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121642985</v>
+        <v>121642556</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,26 +5329,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5364,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>474703</v>
+        <v>475112</v>
       </c>
       <c r="R45" t="n">
-        <v>6784764</v>
+        <v>6784581</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,7 +5405,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5427,7 +5423,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642987</v>
+        <v>121642490</v>
       </c>
       <c r="B46" t="n">
         <v>78616</v>
@@ -5470,10 +5466,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>474688</v>
+        <v>475112</v>
       </c>
       <c r="R46" t="n">
-        <v>6784772</v>
+        <v>6784571</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5533,10 +5529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121642648</v>
+        <v>121643093</v>
       </c>
       <c r="B47" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5549,31 +5545,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5581,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>475130</v>
+        <v>474640</v>
       </c>
       <c r="R47" t="n">
-        <v>6784606</v>
+        <v>6784795</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5625,6 +5616,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5643,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121641316</v>
+        <v>121642499</v>
       </c>
       <c r="B48" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5659,31 +5651,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5691,10 +5678,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475090</v>
+        <v>475105</v>
       </c>
       <c r="R48" t="n">
-        <v>6784447</v>
+        <v>6784582</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5735,6 +5722,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5753,10 +5741,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642746</v>
+        <v>121642403</v>
       </c>
       <c r="B49" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5769,26 +5757,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5796,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475079</v>
+        <v>475125</v>
       </c>
       <c r="R49" t="n">
-        <v>6784712</v>
+        <v>6784471</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5840,7 +5833,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5859,10 +5851,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121641324</v>
+        <v>121642746</v>
       </c>
       <c r="B50" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5875,31 +5867,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5907,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475075</v>
+        <v>475079</v>
       </c>
       <c r="R50" t="n">
-        <v>6784468</v>
+        <v>6784712</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5951,6 +5938,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5969,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121643182</v>
+        <v>121643049</v>
       </c>
       <c r="B51" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5985,31 +5973,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6017,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474609</v>
+        <v>474659</v>
       </c>
       <c r="R51" t="n">
-        <v>6784770</v>
+        <v>6784800</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6061,6 +6044,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6079,10 +6063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642847</v>
+        <v>121642742</v>
       </c>
       <c r="B52" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6095,26 +6079,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6122,10 +6111,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>474825</v>
+        <v>475084</v>
       </c>
       <c r="R52" t="n">
-        <v>6784805</v>
+        <v>6784706</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6166,7 +6155,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6185,7 +6173,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642306</v>
+        <v>121643189</v>
       </c>
       <c r="B53" t="n">
         <v>78616</v>
@@ -6228,10 +6216,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>475127</v>
+        <v>474585</v>
       </c>
       <c r="R53" t="n">
-        <v>6784476</v>
+        <v>6784789</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6291,7 +6279,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642587</v>
+        <v>121642869</v>
       </c>
       <c r="B54" t="n">
         <v>78616</v>
@@ -6334,10 +6322,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>475118</v>
+        <v>474808</v>
       </c>
       <c r="R54" t="n">
-        <v>6784585</v>
+        <v>6784785</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6397,7 +6385,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121643189</v>
+        <v>121642593</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6440,10 +6428,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474585</v>
+        <v>475125</v>
       </c>
       <c r="R55" t="n">
-        <v>6784789</v>
+        <v>6784604</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6503,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121643090</v>
+        <v>121642881</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6519,26 +6507,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6546,10 +6539,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474641</v>
+        <v>474805</v>
       </c>
       <c r="R56" t="n">
-        <v>6784795</v>
+        <v>6784786</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6590,7 +6583,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6609,10 +6601,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642976</v>
+        <v>121642894</v>
       </c>
       <c r="B57" t="n">
-        <v>78650</v>
+        <v>90728</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6625,25 +6617,29 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6652,10 +6648,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474731</v>
+        <v>474806</v>
       </c>
       <c r="R57" t="n">
-        <v>6784765</v>
+        <v>6784787</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6715,10 +6711,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642729</v>
+        <v>121642308</v>
       </c>
       <c r="B58" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6731,26 +6727,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6758,10 +6759,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475088</v>
+        <v>475127</v>
       </c>
       <c r="R58" t="n">
-        <v>6784704</v>
+        <v>6784476</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6802,7 +6803,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642921</v>
+        <v>121642506</v>
       </c>
       <c r="B59" t="n">
-        <v>90728</v>
+        <v>90748</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6837,24 +6837,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6868,10 +6872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>474804</v>
+        <v>475110</v>
       </c>
       <c r="R59" t="n">
-        <v>6784818</v>
+        <v>6784578</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6931,10 +6935,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121642860</v>
+        <v>121642755</v>
       </c>
       <c r="B60" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6947,29 +6951,25 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>474820</v>
+        <v>475045</v>
       </c>
       <c r="R60" t="n">
-        <v>6784784</v>
+        <v>6784754</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7041,7 +7041,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121643037</v>
+        <v>121642712</v>
       </c>
       <c r="B61" t="n">
         <v>57357</v>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>474681</v>
+        <v>475147</v>
       </c>
       <c r="R61" t="n">
-        <v>6784796</v>
+        <v>6784617</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807181</v>
+        <v>121807149</v>
       </c>
       <c r="B63" t="n">
         <v>78616</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475055</v>
+        <v>475105</v>
       </c>
       <c r="R63" t="n">
-        <v>6784636</v>
+        <v>6784482</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807130</v>
+        <v>121807181</v>
       </c>
       <c r="B64" t="n">
         <v>78616</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475111</v>
+        <v>475055</v>
       </c>
       <c r="R64" t="n">
-        <v>6784416</v>
+        <v>6784636</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807149</v>
+        <v>121807130</v>
       </c>
       <c r="B65" t="n">
         <v>78616</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475105</v>
+        <v>475111</v>
       </c>
       <c r="R65" t="n">
-        <v>6784482</v>
+        <v>6784416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642921</v>
+        <v>121642666</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,33 +1229,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1264,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474804</v>
+        <v>475136</v>
       </c>
       <c r="R7" t="n">
-        <v>6784818</v>
+        <v>6784615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121642964</v>
+        <v>121643103</v>
       </c>
       <c r="B8" t="n">
-        <v>78650</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474746</v>
+        <v>474609</v>
       </c>
       <c r="R8" t="n">
-        <v>6784772</v>
+        <v>6784770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121643103</v>
+        <v>121642267</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,26 +1445,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1476,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474609</v>
+        <v>475081</v>
       </c>
       <c r="R9" t="n">
-        <v>6784770</v>
+        <v>6784478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642666</v>
+        <v>121642921</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,29 +1551,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1582,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475136</v>
+        <v>474804</v>
       </c>
       <c r="R10" t="n">
-        <v>6784615</v>
+        <v>6784818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642267</v>
+        <v>121642964</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,31 +1665,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475081</v>
+        <v>474746</v>
       </c>
       <c r="R11" t="n">
-        <v>6784478</v>
+        <v>6784772</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642987</v>
+        <v>121642587</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>474688</v>
+        <v>475118</v>
       </c>
       <c r="R18" t="n">
-        <v>6784772</v>
+        <v>6784585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642587</v>
+        <v>121642987</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475118</v>
+        <v>474688</v>
       </c>
       <c r="R19" t="n">
-        <v>6784585</v>
+        <v>6784772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642482</v>
+        <v>121642718</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,29 +2843,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2875,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475111</v>
+        <v>475154</v>
       </c>
       <c r="R22" t="n">
-        <v>6784565</v>
+        <v>6784610</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2941,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642718</v>
+        <v>121642482</v>
       </c>
       <c r="B23" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,33 +2957,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475154</v>
+        <v>475111</v>
       </c>
       <c r="R23" t="n">
-        <v>6784610</v>
+        <v>6784565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121641316</v>
+        <v>121642601</v>
       </c>
       <c r="B25" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3173,31 +3173,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3205,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475090</v>
+        <v>475129</v>
       </c>
       <c r="R25" t="n">
-        <v>6784447</v>
+        <v>6784603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,6 +3244,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3267,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642601</v>
+        <v>121642769</v>
       </c>
       <c r="B26" t="n">
         <v>78616</v>
@@ -3310,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475129</v>
+        <v>475021</v>
       </c>
       <c r="R26" t="n">
-        <v>6784603</v>
+        <v>6784769</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3373,7 +3369,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642769</v>
+        <v>121642928</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3416,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>475021</v>
+        <v>474760</v>
       </c>
       <c r="R27" t="n">
-        <v>6784769</v>
+        <v>6784798</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,10 +3475,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642928</v>
+        <v>121642860</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3495,25 +3491,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474760</v>
+        <v>474820</v>
       </c>
       <c r="R28" t="n">
-        <v>6784798</v>
+        <v>6784784</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121642860</v>
+        <v>121643090</v>
       </c>
       <c r="B29" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3601,29 +3601,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -3632,10 +3628,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474820</v>
+        <v>474641</v>
       </c>
       <c r="R29" t="n">
-        <v>6784784</v>
+        <v>6784795</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121643090</v>
+        <v>121641316</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,26 +3707,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3738,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474641</v>
+        <v>475090</v>
       </c>
       <c r="R30" t="n">
-        <v>6784795</v>
+        <v>6784447</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3782,7 +3783,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -6173,10 +6173,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121643189</v>
+        <v>121642881</v>
       </c>
       <c r="B53" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,26 +6189,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6216,10 +6221,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474585</v>
+        <v>474805</v>
       </c>
       <c r="R53" t="n">
-        <v>6784789</v>
+        <v>6784786</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6260,7 +6265,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6279,7 +6283,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121642869</v>
+        <v>121643189</v>
       </c>
       <c r="B54" t="n">
         <v>78616</v>
@@ -6322,10 +6326,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474808</v>
+        <v>474585</v>
       </c>
       <c r="R54" t="n">
-        <v>6784785</v>
+        <v>6784789</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6385,7 +6389,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642593</v>
+        <v>121642869</v>
       </c>
       <c r="B55" t="n">
         <v>78616</v>
@@ -6428,10 +6432,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>475125</v>
+        <v>474808</v>
       </c>
       <c r="R55" t="n">
-        <v>6784604</v>
+        <v>6784785</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,10 +6495,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642881</v>
+        <v>121642593</v>
       </c>
       <c r="B56" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6507,31 +6511,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6539,10 +6538,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>474805</v>
+        <v>475125</v>
       </c>
       <c r="R56" t="n">
-        <v>6784786</v>
+        <v>6784604</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,6 +6582,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121642729</v>
+        <v>121642942</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475088</v>
+        <v>474753</v>
       </c>
       <c r="R2" t="n">
-        <v>6784704</v>
+        <v>6784789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121642673</v>
+        <v>121643189</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475137</v>
+        <v>474585</v>
       </c>
       <c r="R3" t="n">
-        <v>6784616</v>
+        <v>6784789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121643037</v>
+        <v>121642587</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474681</v>
+        <v>475118</v>
       </c>
       <c r="R4" t="n">
-        <v>6784796</v>
+        <v>6784585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121642260</v>
+        <v>121642964</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78663</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,31 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475080</v>
+        <v>474746</v>
       </c>
       <c r="R5" t="n">
-        <v>6784480</v>
+        <v>6784772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121642300</v>
+        <v>121642650</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475106</v>
+        <v>475130</v>
       </c>
       <c r="R6" t="n">
-        <v>6784487</v>
+        <v>6784606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121642666</v>
+        <v>121642660</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
+        <v>78629</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475136</v>
+        <v>475110</v>
       </c>
       <c r="R7" t="n">
-        <v>6784615</v>
+        <v>6784606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121643103</v>
+        <v>121642666</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90707</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474609</v>
+        <v>475136</v>
       </c>
       <c r="R8" t="n">
-        <v>6784770</v>
+        <v>6784615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121642267</v>
+        <v>121642881</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475081</v>
+        <v>474805</v>
       </c>
       <c r="R9" t="n">
-        <v>6784478</v>
+        <v>6784786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121642921</v>
+        <v>121642308</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>57365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,30 +1543,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474804</v>
+        <v>475127</v>
       </c>
       <c r="R10" t="n">
-        <v>6784818</v>
+        <v>6784476</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1619,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1649,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121642964</v>
+        <v>121642985</v>
       </c>
       <c r="B11" t="n">
-        <v>78650</v>
+        <v>78629</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474746</v>
+        <v>474703</v>
       </c>
       <c r="R11" t="n">
-        <v>6784772</v>
+        <v>6784764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121643023</v>
+        <v>121643090</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474686</v>
+        <v>474641</v>
       </c>
       <c r="R12" t="n">
-        <v>6784780</v>
+        <v>6784795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1861,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121642603</v>
+        <v>121642482</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,26 +1865,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1904,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475130</v>
+        <v>475111</v>
       </c>
       <c r="R13" t="n">
-        <v>6784603</v>
+        <v>6784565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,7 +1941,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121642803</v>
+        <v>121642781</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474986</v>
+        <v>475004</v>
       </c>
       <c r="R14" t="n">
-        <v>6784798</v>
+        <v>6784792</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121642791</v>
+        <v>121641430</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,26 +2085,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474995</v>
+        <v>475085</v>
       </c>
       <c r="R15" t="n">
-        <v>6784797</v>
+        <v>6784456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2165,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121642751</v>
+        <v>121643037</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,26 +2199,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475056</v>
+        <v>474681</v>
       </c>
       <c r="R16" t="n">
-        <v>6784745</v>
+        <v>6784796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,7 +2275,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2289,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121642660</v>
+        <v>121642791</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475110</v>
+        <v>474995</v>
       </c>
       <c r="R17" t="n">
-        <v>6784606</v>
+        <v>6784797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121642587</v>
+        <v>121642869</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475118</v>
+        <v>474808</v>
       </c>
       <c r="R18" t="n">
-        <v>6784585</v>
+        <v>6784785</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121642987</v>
+        <v>121642593</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2544,10 +2548,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474688</v>
+        <v>475125</v>
       </c>
       <c r="R19" t="n">
-        <v>6784772</v>
+        <v>6784604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121642761</v>
+        <v>121642499</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2623,31 +2627,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475033</v>
+        <v>475105</v>
       </c>
       <c r="R20" t="n">
-        <v>6784752</v>
+        <v>6784582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,6 +2698,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121642648</v>
+        <v>121642493</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475130</v>
+        <v>475116</v>
       </c>
       <c r="R21" t="n">
-        <v>6784606</v>
+        <v>6784570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121642718</v>
+        <v>121642894</v>
       </c>
       <c r="B22" t="n">
-        <v>57510</v>
+        <v>90742</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,35 +2843,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2879,10 +2874,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475154</v>
+        <v>474806</v>
       </c>
       <c r="R22" t="n">
-        <v>6784610</v>
+        <v>6784787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,6 +2918,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2941,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121642482</v>
+        <v>121643023</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,31 +2953,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2989,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475111</v>
+        <v>474686</v>
       </c>
       <c r="R23" t="n">
-        <v>6784565</v>
+        <v>6784780</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,6 +3024,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3051,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121642976</v>
+        <v>121642306</v>
       </c>
       <c r="B24" t="n">
-        <v>78650</v>
+        <v>78629</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3094,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474731</v>
+        <v>475127</v>
       </c>
       <c r="R24" t="n">
-        <v>6784765</v>
+        <v>6784476</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3157,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121642601</v>
+        <v>121642751</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>475129</v>
+        <v>475056</v>
       </c>
       <c r="R25" t="n">
-        <v>6784603</v>
+        <v>6784745</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121642769</v>
+        <v>121642987</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>475021</v>
+        <v>474688</v>
       </c>
       <c r="R26" t="n">
-        <v>6784769</v>
+        <v>6784772</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,10 +3361,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121642928</v>
+        <v>121642761</v>
       </c>
       <c r="B27" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,26 +3377,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3412,10 +3409,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474760</v>
+        <v>475033</v>
       </c>
       <c r="R27" t="n">
-        <v>6784798</v>
+        <v>6784752</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,7 +3453,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3475,10 +3471,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121642860</v>
+        <v>121642556</v>
       </c>
       <c r="B28" t="n">
-        <v>90746</v>
+        <v>57365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3491,30 +3487,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3522,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474820</v>
+        <v>475112</v>
       </c>
       <c r="R28" t="n">
-        <v>6784784</v>
+        <v>6784581</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,7 +3563,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3585,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121643090</v>
+        <v>121642712</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3601,26 +3597,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3628,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474641</v>
+        <v>475147</v>
       </c>
       <c r="R29" t="n">
-        <v>6784795</v>
+        <v>6784617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3672,7 +3673,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121641316</v>
+        <v>121642735</v>
       </c>
       <c r="B30" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3707,31 +3707,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3739,10 +3734,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>475090</v>
+        <v>475086</v>
       </c>
       <c r="R30" t="n">
-        <v>6784447</v>
+        <v>6784704</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,6 +3778,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3801,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121642306</v>
+        <v>121642742</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3817,26 +3813,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3844,10 +3845,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>475127</v>
+        <v>475084</v>
       </c>
       <c r="R31" t="n">
-        <v>6784476</v>
+        <v>6784706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3889,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121641324</v>
+        <v>121642260</v>
       </c>
       <c r="B32" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>475075</v>
+        <v>475080</v>
       </c>
       <c r="R32" t="n">
-        <v>6784468</v>
+        <v>6784480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121643182</v>
+        <v>121642490</v>
       </c>
       <c r="B33" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4033,31 +4033,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4065,10 +4060,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474609</v>
+        <v>475112</v>
       </c>
       <c r="R33" t="n">
-        <v>6784770</v>
+        <v>6784571</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4109,6 +4104,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,10 +4123,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121642955</v>
+        <v>121641324</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,26 +4139,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4170,10 +4171,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474754</v>
+        <v>475075</v>
       </c>
       <c r="R34" t="n">
-        <v>6784810</v>
+        <v>6784468</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4214,7 +4215,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121642650</v>
+        <v>121642269</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,26 +4249,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4276,10 +4281,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>475130</v>
+        <v>475102</v>
       </c>
       <c r="R35" t="n">
-        <v>6784606</v>
+        <v>6784483</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,7 +4325,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4339,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121642735</v>
+        <v>121642729</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4382,7 +4386,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>475086</v>
+        <v>475088</v>
       </c>
       <c r="R36" t="n">
         <v>6784704</v>
@@ -4445,10 +4449,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121642493</v>
+        <v>121642673</v>
       </c>
       <c r="B37" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4461,31 +4465,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4493,10 +4492,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>475116</v>
+        <v>475137</v>
       </c>
       <c r="R37" t="n">
-        <v>6784570</v>
+        <v>6784616</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,6 +4536,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121642781</v>
+        <v>121642648</v>
       </c>
       <c r="B38" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>475004</v>
+        <v>475130</v>
       </c>
       <c r="R38" t="n">
-        <v>6784792</v>
+        <v>6784606</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121641430</v>
+        <v>121642267</v>
       </c>
       <c r="B39" t="n">
-        <v>57510</v>
+        <v>57365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,33 +4681,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4717,10 +4713,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>475085</v>
+        <v>475081</v>
       </c>
       <c r="R39" t="n">
-        <v>6784456</v>
+        <v>6784478</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4779,10 +4775,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121642942</v>
+        <v>121642921</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>90742</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4795,25 +4791,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>474753</v>
+        <v>474804</v>
       </c>
       <c r="R40" t="n">
-        <v>6784789</v>
+        <v>6784818</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642847</v>
+        <v>121642403</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,26 +4901,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4928,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>474825</v>
+        <v>475125</v>
       </c>
       <c r="R41" t="n">
-        <v>6784805</v>
+        <v>6784471</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4977,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +4995,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121642985</v>
+        <v>121642601</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5034,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>474703</v>
+        <v>475129</v>
       </c>
       <c r="R42" t="n">
-        <v>6784764</v>
+        <v>6784603</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,10 +5101,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121643203</v>
+        <v>121643093</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5140,10 +5144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474542</v>
+        <v>474640</v>
       </c>
       <c r="R43" t="n">
-        <v>6784809</v>
+        <v>6784795</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,10 +5207,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121642269</v>
+        <v>121642769</v>
       </c>
       <c r="B44" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,31 +5223,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5251,10 +5250,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>475102</v>
+        <v>475021</v>
       </c>
       <c r="R44" t="n">
-        <v>6784483</v>
+        <v>6784769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,6 +5294,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5313,10 +5313,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121642556</v>
+        <v>121642603</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5329,31 +5329,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>475112</v>
+        <v>475130</v>
       </c>
       <c r="R45" t="n">
-        <v>6784581</v>
+        <v>6784603</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5405,6 +5400,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5423,10 +5419,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121642490</v>
+        <v>121642755</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5466,10 +5462,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>475112</v>
+        <v>475045</v>
       </c>
       <c r="R46" t="n">
-        <v>6784571</v>
+        <v>6784754</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5529,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121643093</v>
+        <v>121642976</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>78663</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5545,21 +5541,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5572,10 +5568,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>474640</v>
+        <v>474731</v>
       </c>
       <c r="R47" t="n">
-        <v>6784795</v>
+        <v>6784765</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,10 +5631,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121642499</v>
+        <v>121642746</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5678,10 +5674,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>475105</v>
+        <v>475079</v>
       </c>
       <c r="R48" t="n">
-        <v>6784582</v>
+        <v>6784712</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,10 +5737,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121642403</v>
+        <v>121642718</v>
       </c>
       <c r="B49" t="n">
-        <v>57357</v>
+        <v>57518</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5757,29 +5753,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>475125</v>
+        <v>475154</v>
       </c>
       <c r="R49" t="n">
-        <v>6784471</v>
+        <v>6784610</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121642746</v>
+        <v>121642847</v>
       </c>
       <c r="B50" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>475079</v>
+        <v>474825</v>
       </c>
       <c r="R50" t="n">
-        <v>6784712</v>
+        <v>6784805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5957,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121643049</v>
+        <v>121642955</v>
       </c>
       <c r="B51" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>474659</v>
+        <v>474754</v>
       </c>
       <c r="R51" t="n">
-        <v>6784800</v>
+        <v>6784810</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6063,10 +6063,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121642742</v>
+        <v>121643203</v>
       </c>
       <c r="B52" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6079,31 +6079,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>475084</v>
+        <v>474542</v>
       </c>
       <c r="R52" t="n">
-        <v>6784706</v>
+        <v>6784809</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6155,6 +6150,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6173,10 +6169,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121642881</v>
+        <v>121643103</v>
       </c>
       <c r="B53" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6189,31 +6185,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6221,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>474805</v>
+        <v>474609</v>
       </c>
       <c r="R53" t="n">
-        <v>6784786</v>
+        <v>6784770</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6265,6 +6256,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6283,10 +6275,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121643189</v>
+        <v>121641316</v>
       </c>
       <c r="B54" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6299,26 +6291,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6326,10 +6323,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>474585</v>
+        <v>475090</v>
       </c>
       <c r="R54" t="n">
-        <v>6784789</v>
+        <v>6784447</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6370,7 +6367,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6389,10 +6385,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121642869</v>
+        <v>121642300</v>
       </c>
       <c r="B55" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6405,26 +6401,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6432,10 +6433,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>474808</v>
+        <v>475106</v>
       </c>
       <c r="R55" t="n">
-        <v>6784785</v>
+        <v>6784487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6476,7 +6477,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6495,10 +6495,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121642593</v>
+        <v>121642928</v>
       </c>
       <c r="B56" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>475125</v>
+        <v>474760</v>
       </c>
       <c r="R56" t="n">
-        <v>6784604</v>
+        <v>6784798</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6601,10 +6601,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121642894</v>
+        <v>121643049</v>
       </c>
       <c r="B57" t="n">
-        <v>90728</v>
+        <v>78629</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6617,29 +6617,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6648,10 +6644,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>474806</v>
+        <v>474659</v>
       </c>
       <c r="R57" t="n">
-        <v>6784787</v>
+        <v>6784800</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6711,10 +6707,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121642308</v>
+        <v>121642506</v>
       </c>
       <c r="B58" t="n">
-        <v>57357</v>
+        <v>90762</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6727,31 +6723,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6759,10 +6758,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>475127</v>
+        <v>475110</v>
       </c>
       <c r="R58" t="n">
-        <v>6784476</v>
+        <v>6784578</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6803,6 +6802,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6821,10 +6821,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121642506</v>
+        <v>121642860</v>
       </c>
       <c r="B59" t="n">
-        <v>90748</v>
+        <v>90760</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6837,28 +6837,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -6872,10 +6868,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>475110</v>
+        <v>474820</v>
       </c>
       <c r="R59" t="n">
-        <v>6784578</v>
+        <v>6784784</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6935,10 +6931,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121642755</v>
+        <v>121642803</v>
       </c>
       <c r="B60" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6951,26 +6947,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6978,10 +6979,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>475045</v>
+        <v>474986</v>
       </c>
       <c r="R60" t="n">
-        <v>6784754</v>
+        <v>6784798</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7022,7 +7023,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7041,10 +7041,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121642712</v>
+        <v>121643182</v>
       </c>
       <c r="B61" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>475147</v>
+        <v>474609</v>
       </c>
       <c r="R61" t="n">
-        <v>6784617</v>
+        <v>6784770</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7154,7 +7154,7 @@
         <v>121724257</v>
       </c>
       <c r="B62" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807149</v>
+        <v>121807181</v>
       </c>
       <c r="B63" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475105</v>
+        <v>475055</v>
       </c>
       <c r="R63" t="n">
-        <v>6784482</v>
+        <v>6784636</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,10 +7369,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807181</v>
+        <v>121807130</v>
       </c>
       <c r="B64" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475055</v>
+        <v>475111</v>
       </c>
       <c r="R64" t="n">
-        <v>6784636</v>
+        <v>6784416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,10 +7475,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807130</v>
+        <v>121807149</v>
       </c>
       <c r="B65" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475111</v>
+        <v>475105</v>
       </c>
       <c r="R65" t="n">
-        <v>6784416</v>
+        <v>6784482</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -4017,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121642490</v>
+        <v>121641324</v>
       </c>
       <c r="B33" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4033,26 +4033,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4060,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>475112</v>
+        <v>475075</v>
       </c>
       <c r="R33" t="n">
-        <v>6784571</v>
+        <v>6784468</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4104,7 +4109,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4123,10 +4127,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121641324</v>
+        <v>121642490</v>
       </c>
       <c r="B34" t="n">
-        <v>57365</v>
+        <v>78629</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,31 +4143,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4171,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>475075</v>
+        <v>475112</v>
       </c>
       <c r="R34" t="n">
-        <v>6784468</v>
+        <v>6784571</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4215,6 +4214,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121642403</v>
+        <v>121642601</v>
       </c>
       <c r="B41" t="n">
-        <v>57365</v>
+        <v>78629</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,31 +4901,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4933,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>475125</v>
+        <v>475129</v>
       </c>
       <c r="R41" t="n">
-        <v>6784471</v>
+        <v>6784603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4977,6 +4972,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4995,7 +4991,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121642601</v>
+        <v>121643093</v>
       </c>
       <c r="B42" t="n">
         <v>78629</v>
@@ -5038,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>475129</v>
+        <v>474640</v>
       </c>
       <c r="R42" t="n">
-        <v>6784603</v>
+        <v>6784795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5101,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121643093</v>
+        <v>121642403</v>
       </c>
       <c r="B43" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5117,26 +5113,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5144,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>474640</v>
+        <v>475125</v>
       </c>
       <c r="R43" t="n">
-        <v>6784795</v>
+        <v>6784471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5188,7 +5189,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -7263,7 +7263,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121807149</v>
+        <v>121807181</v>
       </c>
       <c r="B63" t="n">
         <v>78645</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>475105</v>
+        <v>475055</v>
       </c>
       <c r="R63" t="n">
-        <v>6784482</v>
+        <v>6784636</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121807130</v>
+        <v>121807149</v>
       </c>
       <c r="B64" t="n">
         <v>78645</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>475111</v>
+        <v>475105</v>
       </c>
       <c r="R64" t="n">
-        <v>6784416</v>
+        <v>6784482</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7475,7 +7475,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121807181</v>
+        <v>121807130</v>
       </c>
       <c r="B65" t="n">
         <v>78645</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>475055</v>
+        <v>475111</v>
       </c>
       <c r="R65" t="n">
-        <v>6784636</v>
+        <v>6784416</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>121641324</v>
       </c>
       <c r="B4" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>121642648</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>121642781</v>
       </c>
       <c r="B15" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>121642556</v>
       </c>
       <c r="B20" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>121642803</v>
       </c>
       <c r="B21" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>121643182</v>
       </c>
       <c r="B23" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>121642761</v>
       </c>
       <c r="B24" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>121642260</v>
       </c>
       <c r="B25" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>121642482</v>
       </c>
       <c r="B27" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>121642308</v>
       </c>
       <c r="B28" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>121642300</v>
       </c>
       <c r="B29" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>121642493</v>
       </c>
       <c r="B36" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>121642269</v>
       </c>
       <c r="B37" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>121642267</v>
       </c>
       <c r="B42" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>121642712</v>
       </c>
       <c r="B43" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>121642881</v>
       </c>
       <c r="B47" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>121642742</v>
       </c>
       <c r="B48" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>121643037</v>
       </c>
       <c r="B57" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>121642403</v>
       </c>
       <c r="B58" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>121641316</v>
       </c>
       <c r="B59" t="n">
-        <v>57365</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 45887-2024 artfynd.xlsx
+++ b/artfynd/A 45887-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>121641324</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>121642648</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>121642781</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>121642556</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>121642803</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>121643182</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>121642761</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>121642260</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>121642482</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>121642308</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>121642300</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>121642493</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>121642269</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>121642267</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>121642712</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>121642881</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>121642742</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>121643037</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>121642403</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>121641316</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
